--- a/PARTNER PERFORMANCE.xlsx
+++ b/PARTNER PERFORMANCE.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="74">
   <si>
     <t>BENGKAYANG|BENGKAYANG</t>
   </si>
@@ -222,6 +222,30 @@
   </si>
   <si>
     <t>NAMA PARTNER</t>
+  </si>
+  <si>
+    <t>Prepaid Rev JULI</t>
+  </si>
+  <si>
+    <t>Primary JULI</t>
+  </si>
+  <si>
+    <t>RGUGA FWA ALL CHANNEL JULI</t>
+  </si>
+  <si>
+    <t>RGUGA-Trad JULI</t>
+  </si>
+  <si>
+    <t>Secondary JULI</t>
+  </si>
+  <si>
+    <t>Tertiary B# JULI</t>
+  </si>
+  <si>
+    <t>Trade Supply JULI</t>
+  </si>
+  <si>
+    <t>VLR_SUBS JULI</t>
   </si>
 </sst>
 </file>
@@ -248,8 +272,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="2"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -264,7 +289,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,13 +322,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -588,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:AX19"/>
+  <dimension ref="A5:BF19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36.90625" style="1" bestFit="1" customWidth="1"/>
@@ -599,204 +625,235 @@
     <col min="6" max="6" width="16.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="32.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="33.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="31.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="28.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="21.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="15.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="20.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="18.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="17.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="18.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="16.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="15.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="14.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="16384" width="8.7265625" style="1"/>
+    <col min="9" max="9" width="15.7265625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7265625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="32.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="31.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="29.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="28.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="28.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.7265625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="20.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17" style="1" customWidth="1"/>
+    <col min="31" max="31" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15" style="1" customWidth="1"/>
+    <col min="38" max="38" width="18.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="15.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="15.36328125" style="1" customWidth="1"/>
+    <col min="45" max="45" width="20.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="18.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="16.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="17.26953125" style="1" customWidth="1"/>
+    <col min="52" max="52" width="18.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="16.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="15.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="14.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="O5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="R5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="S5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="T5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="U5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="T5" s="3" t="s">
+      <c r="V5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="U5" s="3" t="s">
+      <c r="W5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="X5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="V5" s="3" t="s">
+      <c r="Y5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="W5" s="3" t="s">
+      <c r="Z5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="X5" s="3" t="s">
+      <c r="AA5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="Y5" s="3" t="s">
+      <c r="AB5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="Z5" s="3" t="s">
+      <c r="AC5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AA5" s="3" t="s">
+      <c r="AD5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB5" s="3" t="s">
+      <c r="AF5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AC5" s="3" t="s">
+      <c r="AG5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="AD5" s="3" t="s">
+      <c r="AH5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AE5" s="3" t="s">
+      <c r="AI5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AF5" s="3" t="s">
+      <c r="AJ5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AG5" s="3" t="s">
+      <c r="AK5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AH5" s="3" t="s">
+      <c r="AM5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AI5" s="3" t="s">
+      <c r="AN5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AJ5" s="3" t="s">
+      <c r="AO5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="AK5" s="3" t="s">
+      <c r="AP5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AL5" s="3" t="s">
+      <c r="AQ5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AM5" s="3" t="s">
+      <c r="AR5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AN5" s="3" t="s">
+      <c r="AT5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AO5" s="3" t="s">
+      <c r="AU5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AP5" s="3" t="s">
+      <c r="AV5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="AQ5" s="3" t="s">
+      <c r="AW5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AR5" s="3" t="s">
+      <c r="AX5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AS5" s="3" t="s">
+      <c r="AY5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AZ5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="AT5" s="3" t="s">
+      <c r="BA5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AU5" s="3" t="s">
+      <c r="BB5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AV5" s="3" t="s">
+      <c r="BC5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AW5" s="3" t="s">
+      <c r="BD5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AX5" s="3" t="s">
+      <c r="BE5" s="4" t="s">
         <v>58</v>
       </c>
+      <c r="BF5" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -822,133 +879,157 @@
         <v>507214049.19737327</v>
       </c>
       <c r="I6" s="3">
+        <v>510028495.30856544</v>
+      </c>
+      <c r="J6" s="3">
         <v>203513.51351351399</v>
       </c>
-      <c r="J6" s="3">
+      <c r="K6" s="3">
         <v>370990.99099099002</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>386307432.43243247</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>4336036.0360360341</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>2132439.6396396412</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>10829729.729729731</v>
       </c>
-      <c r="O6" s="3">
-        <v>0</v>
-      </c>
       <c r="P6" s="3">
-        <v>0</v>
+        <v>8936545.9459459446</v>
       </c>
       <c r="Q6" s="3">
         <v>0</v>
       </c>
       <c r="R6" s="3">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3">
         <v>2</v>
       </c>
-      <c r="S6" s="3">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3">
+      <c r="U6" s="3">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3">
         <v>4</v>
       </c>
-      <c r="U6" s="3">
+      <c r="W6" s="3">
+        <v>2</v>
+      </c>
+      <c r="X6" s="3">
         <v>119</v>
       </c>
-      <c r="V6" s="3">
+      <c r="Y6" s="3">
         <v>160</v>
       </c>
-      <c r="W6" s="3">
+      <c r="Z6" s="3">
         <v>403</v>
       </c>
-      <c r="X6" s="3">
+      <c r="AA6" s="3">
         <v>532</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="AB6" s="3">
         <v>415</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="AC6" s="3">
         <v>552</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AD6" s="3">
+        <v>488</v>
+      </c>
+      <c r="AE6" s="3">
         <v>35808378.378378376</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AF6" s="3">
         <v>39277297.297297299</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AG6" s="3">
         <v>482659423.42342341</v>
       </c>
-      <c r="AD6" s="3">
+      <c r="AH6" s="3">
         <v>49057567.567567565</v>
       </c>
-      <c r="AE6" s="3">
+      <c r="AI6" s="3">
         <v>75839196.396396399</v>
       </c>
-      <c r="AF6" s="3">
+      <c r="AJ6" s="3">
         <v>93100225.225225225</v>
       </c>
-      <c r="AG6" s="3">
+      <c r="AK6" s="3">
+        <v>204066018.01801801</v>
+      </c>
+      <c r="AL6" s="3">
         <v>252829513.51351351</v>
       </c>
-      <c r="AH6" s="3">
+      <c r="AM6" s="3">
         <v>242080702.7027027</v>
       </c>
-      <c r="AI6" s="3">
+      <c r="AN6" s="3">
         <v>277503809.009009</v>
       </c>
-      <c r="AJ6" s="3">
+      <c r="AO6" s="3">
         <v>270568565.76576579</v>
       </c>
-      <c r="AK6" s="3">
+      <c r="AP6" s="3">
         <v>269897936.93693691</v>
       </c>
-      <c r="AL6" s="3">
+      <c r="AQ6" s="3">
         <v>239724342.34234235</v>
       </c>
-      <c r="AM6" s="3">
+      <c r="AR6" s="3">
+        <v>251169441.44144145</v>
+      </c>
+      <c r="AS6" s="3">
         <v>38450680.180180185</v>
       </c>
-      <c r="AN6" s="3">
+      <c r="AT6" s="3">
         <v>39688783.783783786</v>
       </c>
-      <c r="AO6" s="3">
+      <c r="AU6" s="3">
         <v>485471396.3963964</v>
       </c>
-      <c r="AP6" s="3">
+      <c r="AV6" s="3">
         <v>49136666.666666664</v>
       </c>
-      <c r="AQ6" s="3">
+      <c r="AW6" s="3">
         <v>81013693.693693697</v>
       </c>
-      <c r="AR6" s="3">
+      <c r="AX6" s="3">
         <v>89537522.522522524</v>
       </c>
-      <c r="AS6" s="3">
+      <c r="AY6" s="3">
+        <v>205267567.56756756</v>
+      </c>
+      <c r="AZ6" s="3">
         <v>8040</v>
       </c>
-      <c r="AT6" s="3">
+      <c r="BA6" s="3">
         <v>8268</v>
       </c>
-      <c r="AU6" s="3">
+      <c r="BB6" s="3">
         <v>8133</v>
       </c>
-      <c r="AV6" s="3">
+      <c r="BC6" s="3">
         <v>8485</v>
       </c>
-      <c r="AW6" s="3">
+      <c r="BD6" s="3">
         <v>10848</v>
       </c>
-      <c r="AX6" s="3">
+      <c r="BE6" s="3">
         <v>7931</v>
       </c>
+      <c r="BF6" s="1">
+        <v>7724</v>
+      </c>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
@@ -974,28 +1055,28 @@
         <v>57031902.113876797</v>
       </c>
       <c r="I7" s="3">
-        <v>0</v>
+        <v>34312438.506123811</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
       </c>
       <c r="K7" s="3">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3">
         <v>713513.51351351396</v>
       </c>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
       <c r="M7" s="3">
         <v>0</v>
       </c>
       <c r="N7" s="3">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
         <v>59459.459459459998</v>
       </c>
-      <c r="O7" s="3">
-        <v>0</v>
-      </c>
       <c r="P7" s="3">
-        <v>0</v>
+        <v>644144.14414414403</v>
       </c>
       <c r="Q7" s="3">
         <v>0</v>
@@ -1010,97 +1091,121 @@
         <v>0</v>
       </c>
       <c r="U7" s="3">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3">
         <v>6</v>
       </c>
-      <c r="V7" s="3">
+      <c r="Y7" s="3">
         <v>3</v>
       </c>
-      <c r="W7" s="3">
+      <c r="Z7" s="3">
         <v>13</v>
       </c>
-      <c r="X7" s="3">
+      <c r="AA7" s="3">
         <v>5</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="AB7" s="3">
         <v>7</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="AC7" s="3">
         <v>8</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AD7" s="3">
+        <v>4</v>
+      </c>
+      <c r="AE7" s="3">
         <v>453153.15315315302</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AF7" s="3">
         <v>176576.576576577</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AG7" s="3">
         <v>794594.59459459502</v>
       </c>
-      <c r="AD7" s="3">
+      <c r="AH7" s="3">
         <v>216216.21621621601</v>
       </c>
-      <c r="AE7" s="3">
+      <c r="AI7" s="3">
         <v>2323423.4234234239</v>
       </c>
-      <c r="AF7" s="3">
+      <c r="AJ7" s="3">
         <v>2081981.981981982</v>
       </c>
-      <c r="AG7" s="3">
+      <c r="AK7" s="3">
+        <v>12310810.81081081</v>
+      </c>
+      <c r="AL7" s="3">
         <v>39438864.864864863</v>
       </c>
-      <c r="AH7" s="3">
+      <c r="AM7" s="3">
         <v>40892414.414414413</v>
       </c>
-      <c r="AI7" s="3">
+      <c r="AN7" s="3">
         <v>38603315.315315314</v>
       </c>
-      <c r="AJ7" s="3">
+      <c r="AO7" s="3">
         <v>36530513.513513513</v>
       </c>
-      <c r="AK7" s="3">
+      <c r="AP7" s="3">
         <v>41422684.684684686</v>
       </c>
-      <c r="AL7" s="3">
+      <c r="AQ7" s="3">
         <v>35097585.585585587</v>
       </c>
-      <c r="AM7" s="3">
+      <c r="AR7" s="3">
+        <v>21179207.207207207</v>
+      </c>
+      <c r="AS7" s="3">
         <v>469369.36936936999</v>
       </c>
-      <c r="AN7" s="3">
+      <c r="AT7" s="3">
         <v>24799009.009009007</v>
       </c>
-      <c r="AO7" s="3">
+      <c r="AU7" s="3">
         <v>794594.59459459502</v>
       </c>
-      <c r="AP7" s="3">
+      <c r="AV7" s="3">
         <v>216216.21621621601</v>
       </c>
-      <c r="AQ7" s="3">
+      <c r="AW7" s="3">
         <v>2323423.4234234239</v>
       </c>
-      <c r="AR7" s="3">
+      <c r="AX7" s="3">
         <v>1982882.8828828831</v>
       </c>
-      <c r="AS7" s="3">
+      <c r="AY7" s="3">
+        <v>11959009.009009007</v>
+      </c>
+      <c r="AZ7" s="3">
         <v>1216</v>
       </c>
-      <c r="AT7" s="3">
+      <c r="BA7" s="3">
         <v>1049</v>
       </c>
-      <c r="AU7" s="3">
+      <c r="BB7" s="3">
         <v>1148</v>
       </c>
-      <c r="AV7" s="3">
+      <c r="BC7" s="3">
         <v>1120</v>
       </c>
-      <c r="AW7" s="3">
+      <c r="BD7" s="3">
         <v>1095</v>
       </c>
-      <c r="AX7" s="3">
+      <c r="BE7" s="3">
         <v>1110</v>
       </c>
+      <c r="BF7" s="1">
+        <v>1527</v>
+      </c>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
@@ -1126,133 +1231,157 @@
         <v>360448313.34807807</v>
       </c>
       <c r="I8" s="3">
+        <v>339951384.80923343</v>
+      </c>
+      <c r="J8" s="3">
         <v>102837.837837838</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1244009.009009009</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1299946578.3783784</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1014535388.2882882</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1663963.963963965</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4584684.6846846826</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
+        <v>5087768.4684684696</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
         <v>5</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
       <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
         <v>1</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>65</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Y8" s="3">
         <v>35</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Z8" s="3">
         <v>83</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AA8" s="3">
         <v>56</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AB8" s="3">
         <v>9</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AC8" s="3">
         <v>31</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AD8" s="3">
+        <v>71</v>
+      </c>
+      <c r="AE8" s="3">
         <v>140672657.65765765</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AF8" s="3">
         <v>55676666.666666672</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AG8" s="3">
         <v>343935509.009009</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AH8" s="3">
         <v>456286036.03603601</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AI8" s="3">
         <v>95671171.171171173</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AJ8" s="3">
         <v>90238843.243243247</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AK8" s="3">
+        <v>103439091.89189188</v>
+      </c>
+      <c r="AL8" s="3">
         <v>111718427.92792793</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AM8" s="3">
         <v>101496851.35135135</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AN8" s="3">
         <v>107538207.2072072</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AO8" s="3">
         <v>107522270.27027027</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AP8" s="3">
         <v>100889360.36036035</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AQ8" s="3">
         <v>108237441.44144145</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AR8" s="3">
+        <v>97111315.315315306</v>
+      </c>
+      <c r="AS8" s="3">
         <v>135877229.72972974</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AT8" s="3">
         <v>51686918.918918923</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AU8" s="3">
         <v>158870405.4054054</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AV8" s="3">
         <v>201043468.46846849</v>
       </c>
-      <c r="AQ8" s="3">
+      <c r="AW8" s="3">
         <v>92234324.324324325</v>
       </c>
-      <c r="AR8" s="3">
+      <c r="AX8" s="3">
         <v>86003513.51351352</v>
       </c>
-      <c r="AS8" s="3">
+      <c r="AY8" s="3">
+        <v>99631081.081081077</v>
+      </c>
+      <c r="AZ8" s="3">
         <v>3688</v>
       </c>
-      <c r="AT8" s="3">
+      <c r="BA8" s="3">
         <v>3602</v>
       </c>
-      <c r="AU8" s="3">
+      <c r="BB8" s="3">
         <v>3462</v>
       </c>
-      <c r="AV8" s="3">
+      <c r="BC8" s="3">
         <v>3640</v>
       </c>
-      <c r="AW8" s="3">
+      <c r="BD8" s="3">
         <v>3775</v>
       </c>
-      <c r="AX8" s="3">
+      <c r="BE8" s="3">
         <v>2027</v>
       </c>
+      <c r="BF8" s="1">
+        <v>3579</v>
+      </c>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1278,34 +1407,34 @@
         <v>221709432.12152934</v>
       </c>
       <c r="I9" s="3">
+        <v>218776646.67133695</v>
+      </c>
+      <c r="J9" s="3">
         <v>588963.96396396297</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>117927.927927928</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>832432.43243243301</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12427027.027027024</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13372972.972972976</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2354954.9549549548</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
       <c r="P9" s="3">
-        <v>0</v>
+        <v>7701126.1261261273</v>
       </c>
       <c r="Q9" s="3">
         <v>0</v>
       </c>
       <c r="R9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3">
         <v>0</v>
@@ -1314,97 +1443,121 @@
         <v>1</v>
       </c>
       <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
+        <v>1</v>
+      </c>
+      <c r="W9" s="3">
+        <v>4</v>
+      </c>
+      <c r="X9" s="3">
         <v>28</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Y9" s="3">
         <v>108</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Z9" s="3">
         <v>41</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AA9" s="3">
         <v>16</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AB9" s="3">
         <v>65</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AC9" s="3">
         <v>48</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AD9" s="3">
+        <v>46</v>
+      </c>
+      <c r="AE9" s="3">
         <v>16853738.738738734</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AF9" s="3">
         <v>14597882.882882884</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AG9" s="3">
         <v>19118198.198198199</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AH9" s="3">
         <v>32209279.27927928</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AI9" s="3">
         <v>67755180.180180177</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AJ9" s="3">
         <v>118357882.88288288</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AK9" s="3">
+        <v>104305630.63063063</v>
+      </c>
+      <c r="AL9" s="3">
         <v>84993513.51351352</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AM9" s="3">
         <v>85767216.216216207</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AN9" s="3">
         <v>86059351.351351365</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AO9" s="3">
         <v>87400207.207207203</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AP9" s="3">
         <v>82731792.792792797</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AQ9" s="3">
         <v>82382234.234234244</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AR9" s="3">
+        <v>80699774.774774775</v>
+      </c>
+      <c r="AS9" s="3">
         <v>16066576.576576576</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AT9" s="3">
         <v>15452072.072072072</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AU9" s="3">
         <v>19869324.324324325</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AV9" s="3">
         <v>31971441.441441439</v>
       </c>
-      <c r="AQ9" s="3">
+      <c r="AW9" s="3">
         <v>68640405.405405402</v>
       </c>
-      <c r="AR9" s="3">
+      <c r="AX9" s="3">
         <v>116400675.67567568</v>
       </c>
-      <c r="AS9" s="3">
+      <c r="AY9" s="3">
+        <v>96526801.801801801</v>
+      </c>
+      <c r="AZ9" s="3">
         <v>3479</v>
       </c>
-      <c r="AT9" s="3">
+      <c r="BA9" s="3">
         <v>3353</v>
       </c>
-      <c r="AU9" s="3">
+      <c r="BB9" s="3">
         <v>3503</v>
       </c>
-      <c r="AV9" s="3">
+      <c r="BC9" s="3">
         <v>3534</v>
       </c>
-      <c r="AW9" s="3">
+      <c r="BD9" s="3">
         <v>3237</v>
       </c>
-      <c r="AX9" s="3">
+      <c r="BE9" s="3">
         <v>3593</v>
       </c>
+      <c r="BF9" s="1">
+        <v>3552</v>
+      </c>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1430,28 +1583,28 @@
         <v>250380619.74018157</v>
       </c>
       <c r="I10" s="3">
+        <v>247513395.90166593</v>
+      </c>
+      <c r="J10" s="3">
         <v>206576.576576577</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>996306.30630630802</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>457257432.43243247</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1063714864.8648649</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5381981.9819819806</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1900000.0000000009</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
       <c r="P10" s="3">
-        <v>0</v>
+        <v>265765.76576576597</v>
       </c>
       <c r="Q10" s="3">
         <v>0</v>
@@ -1463,100 +1616,124 @@
         <v>0</v>
       </c>
       <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
         <v>1</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
+        <v>1</v>
+      </c>
+      <c r="X10" s="3">
         <v>40</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Y10" s="3">
         <v>63</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Z10" s="3">
         <v>97</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AA10" s="3">
         <v>36</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AB10" s="3">
         <v>25</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AC10" s="3">
         <v>57</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AD10" s="3">
+        <v>28</v>
+      </c>
+      <c r="AE10" s="3">
         <v>16446936.936936937</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AF10" s="3">
         <v>17774864.864864867</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AG10" s="3">
         <v>21434909.909909911</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AH10" s="3">
         <v>26308468.468468469</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AI10" s="3">
         <v>27991216.216216218</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AJ10" s="3">
         <v>27848198.198198196</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AK10" s="3">
+        <v>41664639.639639638</v>
+      </c>
+      <c r="AL10" s="3">
         <v>113496135.13513513</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AM10" s="3">
         <v>113179279.27927928</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AN10" s="3">
         <v>119714324.32432432</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AO10" s="3">
         <v>112842799.0990991</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AP10" s="3">
         <v>112275783.78378379</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AQ10" s="3">
         <v>108577927.92792793</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AR10" s="3">
+        <v>104389837.83783785</v>
+      </c>
+      <c r="AS10" s="3">
         <v>15685315.315315315</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AT10" s="3">
         <v>16278648.648648648</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AU10" s="3">
         <v>18936576.576576576</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AV10" s="3">
         <v>19900180.180180181</v>
       </c>
-      <c r="AQ10" s="3">
+      <c r="AW10" s="3">
         <v>26888513.513513513</v>
       </c>
-      <c r="AR10" s="3">
+      <c r="AX10" s="3">
         <v>26167837.837837838</v>
       </c>
-      <c r="AS10" s="3">
+      <c r="AY10" s="3">
+        <v>40067882.882882878</v>
+      </c>
+      <c r="AZ10" s="3">
         <v>2881</v>
       </c>
-      <c r="AT10" s="3">
+      <c r="BA10" s="3">
         <v>2710</v>
       </c>
-      <c r="AU10" s="3">
+      <c r="BB10" s="3">
         <v>2948</v>
       </c>
-      <c r="AV10" s="3">
+      <c r="BC10" s="3">
         <v>2985</v>
       </c>
-      <c r="AW10" s="3">
+      <c r="BD10" s="3">
         <v>2573</v>
       </c>
-      <c r="AX10" s="3">
+      <c r="BE10" s="3">
         <v>3004</v>
       </c>
+      <c r="BF10" s="1">
+        <v>3081</v>
+      </c>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -1582,133 +1759,157 @@
         <v>895326319.76671219</v>
       </c>
       <c r="I11" s="3">
+        <v>845331062.05816829</v>
+      </c>
+      <c r="J11" s="3">
         <v>638506009.90990984</v>
       </c>
-      <c r="J11" s="3">
+      <c r="K11" s="3">
         <v>822941764.86486495</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="3">
         <v>638930528.82882881</v>
       </c>
-      <c r="L11" s="3">
+      <c r="M11" s="3">
         <v>548376944.14414418</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>4736872.9729729686</v>
       </c>
-      <c r="N11" s="3">
+      <c r="O11" s="3">
         <v>42265579.279279277</v>
       </c>
-      <c r="O11" s="3">
-        <v>0</v>
-      </c>
       <c r="P11" s="3">
+        <v>44588547.747747749</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0</v>
+      </c>
+      <c r="R11" s="3">
         <v>3</v>
       </c>
-      <c r="Q11" s="3">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3">
+      <c r="S11" s="3">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3">
         <v>2</v>
       </c>
-      <c r="S11" s="3">
-        <v>0</v>
-      </c>
-      <c r="T11" s="3">
+      <c r="U11" s="3">
+        <v>0</v>
+      </c>
+      <c r="V11" s="3">
         <v>9</v>
       </c>
-      <c r="U11" s="3">
+      <c r="W11" s="3">
+        <v>2</v>
+      </c>
+      <c r="X11" s="3">
         <v>517</v>
       </c>
-      <c r="V11" s="3">
+      <c r="Y11" s="3">
         <v>478</v>
       </c>
-      <c r="W11" s="3">
+      <c r="Z11" s="3">
         <v>1197</v>
       </c>
-      <c r="X11" s="3">
+      <c r="AA11" s="3">
         <v>1029</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="AB11" s="3">
         <v>666</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="AC11" s="3">
         <v>913</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AD11" s="3">
+        <v>1436</v>
+      </c>
+      <c r="AE11" s="3">
         <v>670162702.70270276</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AF11" s="3">
         <v>679806493.69369364</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AG11" s="3">
         <v>604098193.69369364</v>
       </c>
-      <c r="AD11" s="3">
+      <c r="AH11" s="3">
         <v>598366390.990991</v>
       </c>
-      <c r="AE11" s="3">
+      <c r="AI11" s="3">
         <v>604745206.30630636</v>
       </c>
-      <c r="AF11" s="3">
+      <c r="AJ11" s="3">
         <v>434344633.33333331</v>
       </c>
-      <c r="AG11" s="3">
+      <c r="AK11" s="3">
+        <v>625995597.29729724</v>
+      </c>
+      <c r="AL11" s="3">
         <v>648350765.76576579</v>
       </c>
-      <c r="AH11" s="3">
+      <c r="AM11" s="3">
         <v>662175596.84684682</v>
       </c>
-      <c r="AI11" s="3">
+      <c r="AN11" s="3">
         <v>702347079.27927923</v>
       </c>
-      <c r="AJ11" s="3">
+      <c r="AO11" s="3">
         <v>608951778.37837839</v>
       </c>
-      <c r="AK11" s="3">
+      <c r="AP11" s="3">
         <v>631184342.34234238</v>
       </c>
-      <c r="AL11" s="3">
+      <c r="AQ11" s="3">
         <v>602764971.17117119</v>
       </c>
-      <c r="AM11" s="3">
+      <c r="AR11" s="3">
+        <v>579324936.93693697</v>
+      </c>
+      <c r="AS11" s="3">
         <v>586018468.46846843</v>
       </c>
-      <c r="AN11" s="3">
+      <c r="AT11" s="3">
         <v>627651666.66666663</v>
       </c>
-      <c r="AO11" s="3">
+      <c r="AU11" s="3">
         <v>507988153.15315318</v>
       </c>
-      <c r="AP11" s="3">
+      <c r="AV11" s="3">
         <v>491883333.33333331</v>
       </c>
-      <c r="AQ11" s="3">
+      <c r="AW11" s="3">
         <v>545409414.41441441</v>
       </c>
-      <c r="AR11" s="3">
+      <c r="AX11" s="3">
         <v>403078783.78378379</v>
       </c>
-      <c r="AS11" s="3">
+      <c r="AY11" s="3">
+        <v>594881711.71171176</v>
+      </c>
+      <c r="AZ11" s="3">
         <v>12944</v>
       </c>
-      <c r="AT11" s="3">
+      <c r="BA11" s="3">
         <v>13539</v>
       </c>
-      <c r="AU11" s="3">
+      <c r="BB11" s="3">
         <v>13340</v>
       </c>
-      <c r="AV11" s="3">
+      <c r="BC11" s="3">
         <v>13326</v>
       </c>
-      <c r="AW11" s="3">
+      <c r="BD11" s="3">
         <v>12671</v>
       </c>
-      <c r="AX11" s="3">
+      <c r="BE11" s="3">
         <v>13401</v>
       </c>
+      <c r="BF11" s="1">
+        <v>13750</v>
+      </c>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
@@ -1734,28 +1935,28 @@
         <v>205866304.78977665</v>
       </c>
       <c r="I12" s="3">
+        <v>201546534.46167859</v>
+      </c>
+      <c r="J12" s="3">
         <v>85090.090090088997</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>38513.513513514001</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9459.4594594589998</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5717117.1171171153</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>103305405.4054054</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>283000900.9009009</v>
       </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
       <c r="P12" s="3">
-        <v>0</v>
+        <v>396291828.82882881</v>
       </c>
       <c r="Q12" s="3">
         <v>0</v>
@@ -1770,97 +1971,121 @@
         <v>0</v>
       </c>
       <c r="U12" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="V12" s="3">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="W12" s="3">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="X12" s="3">
         <v>42</v>
       </c>
       <c r="Y12" s="3">
+        <v>229</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>68</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>42</v>
+      </c>
+      <c r="AB12" s="3">
         <v>57</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AC12" s="3">
         <v>31</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AD12" s="3">
+        <v>68</v>
+      </c>
+      <c r="AE12" s="3">
         <v>34624189.189189196</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AF12" s="3">
         <v>28234009.009009007</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AG12" s="3">
         <v>23812612.612612613</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AH12" s="3">
         <v>35304504.504504502</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AI12" s="3">
         <v>49787387.387387387</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AJ12" s="3">
         <v>47238288.288288288</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AK12" s="3">
+        <v>111109459.45945945</v>
+      </c>
+      <c r="AL12" s="3">
         <v>141530813.51351351</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AM12" s="3">
         <v>147375786.03603604</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AN12" s="3">
         <v>156720349.54954955</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AO12" s="3">
         <v>146406531.53153151</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AP12" s="3">
         <v>159118252.25225225</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AQ12" s="3">
         <v>141919810.8108108</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AR12" s="3">
+        <v>135319693.6936937</v>
+      </c>
+      <c r="AS12" s="3">
         <v>28677585.585585583</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AT12" s="3">
         <v>22354144.144144148</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AU12" s="3">
         <v>23202252.252252251</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AV12" s="3">
         <v>32816126.126126129</v>
       </c>
-      <c r="AQ12" s="3">
+      <c r="AW12" s="3">
         <v>19275135.135135133</v>
       </c>
-      <c r="AR12" s="3">
+      <c r="AX12" s="3">
         <v>45052972.972972974</v>
       </c>
-      <c r="AS12" s="3">
+      <c r="AY12" s="3">
+        <v>69285585.585585579</v>
+      </c>
+      <c r="AZ12" s="3">
         <v>4845</v>
       </c>
-      <c r="AT12" s="3">
+      <c r="BA12" s="3">
         <v>4158</v>
       </c>
-      <c r="AU12" s="3">
+      <c r="BB12" s="3">
         <v>4484</v>
       </c>
-      <c r="AV12" s="3">
+      <c r="BC12" s="3">
         <v>4541</v>
       </c>
-      <c r="AW12" s="3">
+      <c r="BD12" s="3">
         <v>4630</v>
       </c>
-      <c r="AX12" s="3">
+      <c r="BE12" s="3">
         <v>4632</v>
       </c>
+      <c r="BF12" s="1">
+        <v>4824</v>
+      </c>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1886,133 +2111,157 @@
         <v>298027076.16491151</v>
       </c>
       <c r="I13" s="3">
+        <v>287413587.27569234</v>
+      </c>
+      <c r="J13" s="3">
         <v>3317500</v>
       </c>
-      <c r="J13" s="3">
+      <c r="K13" s="3">
         <v>4828963.9639639622</v>
       </c>
-      <c r="K13" s="3">
+      <c r="L13" s="3">
         <v>3683333.333333333</v>
       </c>
-      <c r="L13" s="3">
+      <c r="M13" s="3">
         <v>1741441.441441441</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <v>5082882.8828828828</v>
       </c>
-      <c r="N13" s="3">
+      <c r="O13" s="3">
         <v>5099099.0990990978</v>
       </c>
-      <c r="O13" s="3">
-        <v>0</v>
-      </c>
       <c r="P13" s="3">
+        <v>6724681.9819819843</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
         <v>5</v>
       </c>
-      <c r="Q13" s="3">
-        <v>0</v>
-      </c>
-      <c r="R13" s="3">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
         <v>1</v>
       </c>
-      <c r="S13" s="3">
-        <v>0</v>
-      </c>
-      <c r="T13" s="3">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
         <v>2</v>
       </c>
-      <c r="U13" s="3">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
         <v>73</v>
       </c>
-      <c r="V13" s="3">
+      <c r="Y13" s="3">
         <v>127</v>
       </c>
-      <c r="W13" s="3">
+      <c r="Z13" s="3">
         <v>121</v>
       </c>
-      <c r="X13" s="3">
+      <c r="AA13" s="3">
         <v>65</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="AB13" s="3">
         <v>15</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="AC13" s="3">
         <v>59</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="AD13" s="3">
+        <v>63</v>
+      </c>
+      <c r="AE13" s="3">
         <v>51839121.621621624</v>
       </c>
-      <c r="AB13" s="3">
+      <c r="AF13" s="3">
         <v>62088198.198198199</v>
       </c>
-      <c r="AC13" s="3">
+      <c r="AG13" s="3">
         <v>71674324.324324325</v>
       </c>
-      <c r="AD13" s="3">
+      <c r="AH13" s="3">
         <v>76762612.612612605</v>
       </c>
-      <c r="AE13" s="3">
+      <c r="AI13" s="3">
         <v>55213513.513513513</v>
       </c>
-      <c r="AF13" s="3">
+      <c r="AJ13" s="3">
         <v>55615315.315315314</v>
       </c>
-      <c r="AG13" s="3">
+      <c r="AK13" s="3">
+        <v>53050210.810810819</v>
+      </c>
+      <c r="AL13" s="3">
         <v>89223153.153153151</v>
       </c>
-      <c r="AH13" s="3">
+      <c r="AM13" s="3">
         <v>87350851.351351351</v>
       </c>
-      <c r="AI13" s="3">
+      <c r="AN13" s="3">
         <v>96104349.54954955</v>
       </c>
-      <c r="AJ13" s="3">
+      <c r="AO13" s="3">
         <v>88084173.873873875</v>
       </c>
-      <c r="AK13" s="3">
+      <c r="AP13" s="3">
         <v>86464783.783783779</v>
       </c>
-      <c r="AL13" s="3">
+      <c r="AQ13" s="3">
         <v>88053180.180180177</v>
       </c>
-      <c r="AM13" s="3">
+      <c r="AR13" s="3">
+        <v>86734216.216216221</v>
+      </c>
+      <c r="AS13" s="3">
         <v>48542576.576576576</v>
       </c>
-      <c r="AN13" s="3">
+      <c r="AT13" s="3">
         <v>53949738.738738738</v>
       </c>
-      <c r="AO13" s="3">
+      <c r="AU13" s="3">
         <v>71818783.783783779</v>
       </c>
-      <c r="AP13" s="3">
+      <c r="AV13" s="3">
         <v>77257333.333333328</v>
       </c>
-      <c r="AQ13" s="3">
+      <c r="AW13" s="3">
         <v>50835405.40540541</v>
       </c>
-      <c r="AR13" s="3">
+      <c r="AX13" s="3">
         <v>51781351.351351351</v>
       </c>
-      <c r="AS13" s="3">
+      <c r="AY13" s="3">
+        <v>47952882.882882878</v>
+      </c>
+      <c r="AZ13" s="3">
         <v>3583</v>
       </c>
-      <c r="AT13" s="3">
+      <c r="BA13" s="3">
         <v>3585</v>
       </c>
-      <c r="AU13" s="3">
+      <c r="BB13" s="3">
         <v>3730</v>
       </c>
-      <c r="AV13" s="3">
+      <c r="BC13" s="3">
         <v>3698</v>
       </c>
-      <c r="AW13" s="3">
+      <c r="BD13" s="3">
         <v>3542</v>
       </c>
-      <c r="AX13" s="3">
+      <c r="BE13" s="3">
         <v>3662</v>
       </c>
+      <c r="BF13" s="1">
+        <v>3415</v>
+      </c>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -2038,28 +2287,28 @@
         <v>490723343.68780494</v>
       </c>
       <c r="I14" s="3">
+        <v>533068956.22284913</v>
+      </c>
+      <c r="J14" s="3">
         <v>1043978150.4504504</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>811331229.72972977</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>18636109.909909911</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12635188.288288288</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>651672918.01801801</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>504025608.1081081</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
-        <v>4</v>
+        <v>17138469.369369369</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -2071,100 +2320,124 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>1</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
+        <v>1</v>
+      </c>
+      <c r="X14" s="3">
         <v>483</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Y14" s="3">
         <v>427</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Z14" s="3">
         <v>1177</v>
       </c>
-      <c r="X14" s="3">
+      <c r="AA14" s="3">
         <v>1010</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AB14" s="3">
         <v>202</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AC14" s="3">
         <v>227</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AD14" s="3">
+        <v>151</v>
+      </c>
+      <c r="AE14" s="3">
         <v>773978333.33333337</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AF14" s="3">
         <v>763466792.7927928</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AG14" s="3">
         <v>823364037.83783782</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AH14" s="3">
         <v>724311539.63963974</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AI14" s="3">
         <v>811996692.7927928</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AJ14" s="3">
         <v>636634596.3963964</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AK14" s="3">
+        <v>821123052.25225234</v>
+      </c>
+      <c r="AL14" s="3">
         <v>205230034.23423424</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AM14" s="3">
         <v>198082139.63963965</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AN14" s="3">
         <v>235105216.21621624</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AO14" s="3">
         <v>208732621.62162164</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AP14" s="3">
         <v>200317034.23423424</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AQ14" s="3">
         <v>184902018.01801801</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AR14" s="3">
+        <v>193444061.26126125</v>
+      </c>
+      <c r="AS14" s="3">
         <v>660584265.76576579</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AT14" s="3">
         <v>734348657.65765762</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AU14" s="3">
         <v>828830720.72072077</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AV14" s="3">
         <v>728851666.66666663</v>
       </c>
-      <c r="AQ14" s="3">
+      <c r="AW14" s="3">
         <v>705261756.75675678</v>
       </c>
-      <c r="AR14" s="3">
+      <c r="AX14" s="3">
         <v>506043243.24324328</v>
       </c>
-      <c r="AS14" s="3">
+      <c r="AY14" s="3">
+        <v>757542027.02702713</v>
+      </c>
+      <c r="AZ14" s="3">
         <v>6875</v>
       </c>
-      <c r="AT14" s="3">
+      <c r="BA14" s="3">
         <v>6717</v>
       </c>
-      <c r="AU14" s="3">
+      <c r="BB14" s="3">
         <v>7141</v>
       </c>
-      <c r="AV14" s="3">
+      <c r="BC14" s="3">
         <v>7116</v>
       </c>
-      <c r="AW14" s="3">
+      <c r="BD14" s="3">
         <v>7539</v>
       </c>
-      <c r="AX14" s="3">
+      <c r="BE14" s="3">
         <v>8252</v>
       </c>
+      <c r="BF14" s="1">
+        <v>7079</v>
+      </c>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -2190,133 +2463,157 @@
         <v>244067144.70361832</v>
       </c>
       <c r="I15" s="3">
+        <v>229537143.34768772</v>
+      </c>
+      <c r="J15" s="3">
         <v>373558.55855855701</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>449189.18918918999</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>545270.27027026995</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3872072.072072072</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3884684.684684685</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1560360.3603603591</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
+        <v>20268.468468469</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
         <v>1</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
         <v>2</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0</v>
-      </c>
       <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>1</v>
+      </c>
+      <c r="X15" s="3">
         <v>185</v>
       </c>
-      <c r="V15" s="3">
+      <c r="Y15" s="3">
         <v>142</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Z15" s="3">
         <v>271</v>
       </c>
-      <c r="X15" s="3">
+      <c r="AA15" s="3">
         <v>207</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AB15" s="3">
         <v>12</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AC15" s="3">
         <v>14</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AD15" s="3">
+        <v>30</v>
+      </c>
+      <c r="AE15" s="3">
         <v>10691756.756756758</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AF15" s="3">
         <v>18032747.747747749</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AG15" s="3">
         <v>9393468.4684684686</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AH15" s="3">
         <v>13405405.405405406</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AI15" s="3">
         <v>3209009.0090090092</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AJ15" s="3">
         <v>22269819.819819819</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AK15" s="3">
+        <v>21335.135135134999</v>
+      </c>
+      <c r="AL15" s="3">
         <v>160495459.45945945</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AM15" s="3">
         <v>159850909.90990993</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AN15" s="3">
         <v>172412645.04504505</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AO15" s="3">
         <v>159028324.32432431</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AP15" s="3">
         <v>149578126.12612611</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AQ15" s="3">
         <v>147227872.07207206</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AR15" s="3">
+        <v>137361405.4054054</v>
+      </c>
+      <c r="AS15" s="3">
         <v>9338828.8288288284</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AT15" s="3">
         <v>18017027.02702703</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AU15" s="3">
         <v>9646396.3963963985</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AV15" s="3">
         <v>13452072.072072072</v>
       </c>
-      <c r="AQ15" s="3">
+      <c r="AW15" s="3">
         <v>3309729.7297297302</v>
       </c>
-      <c r="AR15" s="3">
+      <c r="AX15" s="3">
         <v>22283603.603603605</v>
       </c>
-      <c r="AS15" s="3">
+      <c r="AY15" s="3">
+        <v>606216.21621621598</v>
+      </c>
+      <c r="AZ15" s="3">
         <v>3639</v>
       </c>
-      <c r="AT15" s="3">
+      <c r="BA15" s="3">
         <v>3492</v>
       </c>
-      <c r="AU15" s="3">
+      <c r="BB15" s="3">
         <v>3753</v>
       </c>
-      <c r="AV15" s="3">
+      <c r="BC15" s="3">
         <v>3758</v>
       </c>
-      <c r="AW15" s="3">
+      <c r="BD15" s="3">
         <v>3447</v>
       </c>
-      <c r="AX15" s="3">
+      <c r="BE15" s="3">
         <v>3755</v>
       </c>
+      <c r="BF15" s="1">
+        <v>3530</v>
+      </c>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
@@ -2342,28 +2639,28 @@
         <v>198416453.34422868</v>
       </c>
       <c r="I16" s="3">
+        <v>190066185.58074287</v>
+      </c>
+      <c r="J16" s="3">
         <v>274774.77477477503</v>
       </c>
-      <c r="J16" s="3">
+      <c r="K16" s="3">
         <v>235765.76576576501</v>
       </c>
-      <c r="K16" s="3">
+      <c r="L16" s="3">
         <v>3336936.936936934</v>
       </c>
-      <c r="L16" s="3">
+      <c r="M16" s="3">
         <v>3814414.4144144142</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>176397306.3063063</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="3">
         <v>147025337.83783782</v>
       </c>
-      <c r="O16" s="3">
-        <v>0</v>
-      </c>
       <c r="P16" s="3">
-        <v>0</v>
+        <v>103184684.68468469</v>
       </c>
       <c r="Q16" s="3">
         <v>0</v>
@@ -2378,97 +2675,121 @@
         <v>0</v>
       </c>
       <c r="U16" s="3">
+        <v>0</v>
+      </c>
+      <c r="V16" s="3">
+        <v>0</v>
+      </c>
+      <c r="W16" s="3">
+        <v>1</v>
+      </c>
+      <c r="X16" s="3">
         <v>14</v>
       </c>
-      <c r="V16" s="3">
+      <c r="Y16" s="3">
         <v>18</v>
       </c>
-      <c r="W16" s="3">
+      <c r="Z16" s="3">
         <v>53</v>
       </c>
-      <c r="X16" s="3">
+      <c r="AA16" s="3">
         <v>40</v>
       </c>
-      <c r="Y16" s="3">
+      <c r="AB16" s="3">
         <v>27</v>
       </c>
-      <c r="Z16" s="3">
+      <c r="AC16" s="3">
         <v>37</v>
       </c>
-      <c r="AA16" s="3">
+      <c r="AD16" s="3">
+        <v>49</v>
+      </c>
+      <c r="AE16" s="3">
         <v>8792792.7927927915</v>
       </c>
-      <c r="AB16" s="3">
+      <c r="AF16" s="3">
         <v>8823153.1531531513</v>
       </c>
-      <c r="AC16" s="3">
+      <c r="AG16" s="3">
         <v>10794594.594594592</v>
       </c>
-      <c r="AD16" s="3">
+      <c r="AH16" s="3">
         <v>9611711.7117117122</v>
       </c>
-      <c r="AE16" s="3">
+      <c r="AI16" s="3">
         <v>77414864.864864871</v>
       </c>
-      <c r="AF16" s="3">
+      <c r="AJ16" s="3">
         <v>107169987.38738739</v>
       </c>
-      <c r="AG16" s="3">
+      <c r="AK16" s="3">
+        <v>34478153.153153151</v>
+      </c>
+      <c r="AL16" s="3">
         <v>71787887.38738738</v>
       </c>
-      <c r="AH16" s="3">
+      <c r="AM16" s="3">
         <v>66822295.045045041</v>
       </c>
-      <c r="AI16" s="3">
+      <c r="AN16" s="3">
         <v>81646585.585585579</v>
       </c>
-      <c r="AJ16" s="3">
+      <c r="AO16" s="3">
         <v>75973052.252252251</v>
       </c>
-      <c r="AK16" s="3">
+      <c r="AP16" s="3">
         <v>76229475.675675675</v>
       </c>
-      <c r="AL16" s="3">
+      <c r="AQ16" s="3">
         <v>72418261.261261269</v>
       </c>
-      <c r="AM16" s="3">
+      <c r="AR16" s="3">
+        <v>72137783.783783779</v>
+      </c>
+      <c r="AS16" s="3">
         <v>8465099.0990991015</v>
       </c>
-      <c r="AN16" s="3">
+      <c r="AT16" s="3">
         <v>7592477.4774774779</v>
       </c>
-      <c r="AO16" s="3">
+      <c r="AU16" s="3">
         <v>12520180.180180177</v>
       </c>
-      <c r="AP16" s="3">
+      <c r="AV16" s="3">
         <v>9154144.1441441439</v>
       </c>
-      <c r="AQ16" s="3">
+      <c r="AW16" s="3">
         <v>18817477.477477476</v>
       </c>
-      <c r="AR16" s="3">
+      <c r="AX16" s="3">
         <v>20870540.540540539</v>
       </c>
-      <c r="AS16" s="3">
+      <c r="AY16" s="3">
+        <v>31856576.576576576</v>
+      </c>
+      <c r="AZ16" s="3">
         <v>3401</v>
       </c>
-      <c r="AT16" s="3">
+      <c r="BA16" s="3">
         <v>3453</v>
       </c>
-      <c r="AU16" s="3">
+      <c r="BB16" s="3">
         <v>3717</v>
       </c>
-      <c r="AV16" s="3">
+      <c r="BC16" s="3">
         <v>3786</v>
       </c>
-      <c r="AW16" s="3">
+      <c r="BD16" s="3">
         <v>5507</v>
       </c>
-      <c r="AX16" s="3">
+      <c r="BE16" s="3">
         <v>3822</v>
       </c>
+      <c r="BF16" s="1">
+        <v>3805</v>
+      </c>
     </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
@@ -2494,133 +2815,157 @@
         <v>124706710.37548444</v>
       </c>
       <c r="I17" s="3">
+        <v>123579774.40923691</v>
+      </c>
+      <c r="J17" s="3">
         <v>97747.747747747999</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>321936.93693693797</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2075675.675675675</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1740540.5405405399</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>471171.17117117101</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2105405.405405404</v>
       </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
       <c r="P17" s="3">
-        <v>0</v>
+        <v>1352702.702702703</v>
       </c>
       <c r="Q17" s="3">
         <v>0</v>
       </c>
       <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
         <v>1</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
       <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3">
         <v>13</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Y17" s="3">
         <v>68</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Z17" s="3">
         <v>66</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AA17" s="3">
         <v>31</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AB17" s="3">
         <v>17</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AC17" s="3">
         <v>48</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AD17" s="3">
+        <v>25</v>
+      </c>
+      <c r="AE17" s="3">
         <v>18822972.97297297</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AF17" s="3">
         <v>12843108.108108109</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AG17" s="3">
         <v>11534234.234234236</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AH17" s="3">
         <v>9440540.5405405313</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AI17" s="3">
         <v>24471171.171171173</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AJ17" s="3">
         <v>34308108.108108103</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AK17" s="3">
+        <v>20226576.576576576</v>
+      </c>
+      <c r="AL17" s="3">
         <v>47596881.081081077</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AM17" s="3">
         <v>48907360.360360362</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AN17" s="3">
         <v>61340953.153153151</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AO17" s="3">
         <v>51499123.423423424</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AP17" s="3">
         <v>54383216.216216214</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AQ17" s="3">
         <v>55297000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AR17" s="3">
+        <v>53152927.927927926</v>
+      </c>
+      <c r="AS17" s="3">
         <v>14111153.153153151</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AT17" s="3">
         <v>12608378.378378378</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AU17" s="3">
         <v>11307387.387387387</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AV17" s="3">
         <v>9557927.9279279206</v>
       </c>
-      <c r="AQ17" s="3">
+      <c r="AW17" s="3">
         <v>24743603.603603605</v>
       </c>
-      <c r="AR17" s="3">
+      <c r="AX17" s="3">
         <v>29474864.864864863</v>
       </c>
-      <c r="AS17" s="3">
+      <c r="AY17" s="3">
+        <v>20739099.0990991</v>
+      </c>
+      <c r="AZ17" s="3">
         <v>2548</v>
       </c>
-      <c r="AT17" s="3">
+      <c r="BA17" s="3">
         <v>2563</v>
       </c>
-      <c r="AU17" s="3">
+      <c r="BB17" s="3">
         <v>3006</v>
       </c>
-      <c r="AV17" s="3">
+      <c r="BC17" s="3">
         <v>2932</v>
       </c>
-      <c r="AW17" s="3">
+      <c r="BD17" s="3">
         <v>3025</v>
       </c>
-      <c r="AX17" s="3">
+      <c r="BE17" s="3">
         <v>2859</v>
       </c>
+      <c r="BF17" s="1">
+        <v>2808</v>
+      </c>
     </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
@@ -2646,133 +2991,157 @@
         <v>431110782.58231896</v>
       </c>
       <c r="I18" s="3">
+        <v>445756632.36136365</v>
+      </c>
+      <c r="J18" s="3">
         <v>297825005.4054054</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>593172914.41441441</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>432353816.21621621</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>584661011.71171176</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4777485.5855855877</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8999099.0990991015</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
       <c r="P18" s="3">
-        <v>0</v>
+        <v>7280018.9189189225</v>
       </c>
       <c r="Q18" s="3">
         <v>0</v>
       </c>
       <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>4</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>3</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>378</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Y18" s="3">
         <v>473</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Z18" s="3">
         <v>677</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AA18" s="3">
         <v>468</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AB18" s="3">
         <v>694</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AC18" s="3">
         <v>1016</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AD18" s="3">
+        <v>1015</v>
+      </c>
+      <c r="AE18" s="3">
         <v>64616126.126126125</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AF18" s="3">
         <v>57526216.216216214</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AG18" s="3">
         <v>68259909.909909919</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AH18" s="3">
         <v>79598198.198198199</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AI18" s="3">
         <v>137399782.88288289</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AJ18" s="3">
         <v>143875450.45045045</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AK18" s="3">
+        <v>181679764.86486486</v>
+      </c>
+      <c r="AL18" s="3">
         <v>247552630.63063061</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AM18" s="3">
         <v>253424531.53153151</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AN18" s="3">
         <v>288917252.25225222</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AO18" s="3">
         <v>235132115.31531534</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AP18" s="3">
         <v>268380423.42342341</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AQ18" s="3">
         <v>259011018.01801801</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AR18" s="3">
+        <v>279009504.5045045</v>
+      </c>
+      <c r="AS18" s="3">
         <v>55377549.54954955</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AT18" s="3">
         <v>53618441.441441439</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AU18" s="3">
         <v>56583513.51351352</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AV18" s="3">
         <v>68058918.918918923</v>
       </c>
-      <c r="AQ18" s="3">
+      <c r="AW18" s="3">
         <v>137662567.56756756</v>
       </c>
-      <c r="AR18" s="3">
+      <c r="AX18" s="3">
         <v>140834549.54954955</v>
       </c>
-      <c r="AS18" s="3">
+      <c r="AY18" s="3">
+        <v>208183063.06306309</v>
+      </c>
+      <c r="AZ18" s="3">
         <v>6609</v>
       </c>
-      <c r="AT18" s="3">
+      <c r="BA18" s="3">
         <v>6595</v>
       </c>
-      <c r="AU18" s="3">
+      <c r="BB18" s="3">
         <v>6748</v>
       </c>
-      <c r="AV18" s="3">
+      <c r="BC18" s="3">
         <v>9658</v>
       </c>
-      <c r="AW18" s="3">
+      <c r="BD18" s="3">
         <v>8834</v>
       </c>
-      <c r="AX18" s="3">
+      <c r="BE18" s="3">
         <v>7861</v>
       </c>
+      <c r="BF18" s="1">
+        <v>7168</v>
+      </c>
     </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
@@ -2798,28 +3167,28 @@
         <v>252288145.25318137</v>
       </c>
       <c r="I19" s="3">
+        <v>239444971.9093622</v>
+      </c>
+      <c r="J19" s="3">
         <v>1299729.7297297299</v>
       </c>
-      <c r="J19" s="3">
+      <c r="K19" s="3">
         <v>620180.18018018</v>
       </c>
-      <c r="K19" s="3">
+      <c r="L19" s="3">
         <v>1156756.756756756</v>
       </c>
-      <c r="L19" s="3">
+      <c r="M19" s="3">
         <v>6994144.1441441393</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="3">
         <v>4467567.567567572</v>
       </c>
-      <c r="N19" s="3">
+      <c r="O19" s="3">
         <v>1938738.738738738</v>
       </c>
-      <c r="O19" s="3">
-        <v>0</v>
-      </c>
       <c r="P19" s="3">
-        <v>0</v>
+        <v>1779947.7477477491</v>
       </c>
       <c r="Q19" s="3">
         <v>0</v>
@@ -2834,94 +3203,118 @@
         <v>0</v>
       </c>
       <c r="U19" s="3">
+        <v>0</v>
+      </c>
+      <c r="V19" s="3">
+        <v>0</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0</v>
+      </c>
+      <c r="X19" s="3">
         <v>25</v>
       </c>
-      <c r="V19" s="3">
+      <c r="Y19" s="3">
         <v>18</v>
       </c>
-      <c r="W19" s="3">
+      <c r="Z19" s="3">
         <v>30</v>
       </c>
-      <c r="X19" s="3">
+      <c r="AA19" s="3">
         <v>37</v>
       </c>
-      <c r="Y19" s="3">
+      <c r="AB19" s="3">
         <v>39</v>
       </c>
-      <c r="Z19" s="3">
+      <c r="AC19" s="3">
         <v>28</v>
       </c>
-      <c r="AA19" s="3">
+      <c r="AD19" s="3">
+        <v>40</v>
+      </c>
+      <c r="AE19" s="3">
         <v>28883783.783783782</v>
       </c>
-      <c r="AB19" s="3">
+      <c r="AF19" s="3">
         <v>42477612.612612613</v>
       </c>
-      <c r="AC19" s="3">
+      <c r="AG19" s="3">
         <v>44288513.513513513</v>
       </c>
-      <c r="AD19" s="3">
+      <c r="AH19" s="3">
         <v>39225675.675675675</v>
       </c>
-      <c r="AE19" s="3">
+      <c r="AI19" s="3">
         <v>51458783.783783786</v>
       </c>
-      <c r="AF19" s="3">
+      <c r="AJ19" s="3">
         <v>44963063.063063063</v>
       </c>
-      <c r="AG19" s="3">
+      <c r="AK19" s="3">
+        <v>52455705.40540541</v>
+      </c>
+      <c r="AL19" s="3">
         <v>109155265.76576576</v>
       </c>
-      <c r="AH19" s="3">
+      <c r="AM19" s="3">
         <v>106279961.7117117</v>
       </c>
-      <c r="AI19" s="3">
+      <c r="AN19" s="3">
         <v>120641801.8018018</v>
       </c>
-      <c r="AJ19" s="3">
+      <c r="AO19" s="3">
         <v>99386009.009009004</v>
       </c>
-      <c r="AK19" s="3">
+      <c r="AP19" s="3">
         <v>99723738.738738731</v>
       </c>
-      <c r="AL19" s="3">
+      <c r="AQ19" s="3">
         <v>89829945.945945948</v>
       </c>
-      <c r="AM19" s="3">
+      <c r="AR19" s="3">
+        <v>83526045.045045033</v>
+      </c>
+      <c r="AS19" s="3">
         <v>34262927.927927926</v>
       </c>
-      <c r="AN19" s="3">
+      <c r="AT19" s="3">
         <v>39493333.333333336</v>
       </c>
-      <c r="AO19" s="3">
+      <c r="AU19" s="3">
         <v>35223603.603603601</v>
       </c>
-      <c r="AP19" s="3">
+      <c r="AV19" s="3">
         <v>42599729.729729727</v>
       </c>
-      <c r="AQ19" s="3">
+      <c r="AW19" s="3">
         <v>50633198.198198199</v>
       </c>
-      <c r="AR19" s="3">
+      <c r="AX19" s="3">
         <v>40236396.396396399</v>
       </c>
-      <c r="AS19" s="3">
+      <c r="AY19" s="3">
+        <v>45674504.504504502</v>
+      </c>
+      <c r="AZ19" s="3">
         <v>3792</v>
       </c>
-      <c r="AT19" s="3">
+      <c r="BA19" s="3">
         <v>3750</v>
       </c>
-      <c r="AU19" s="3">
+      <c r="BB19" s="3">
         <v>3745</v>
       </c>
-      <c r="AV19" s="3">
+      <c r="BC19" s="3">
         <v>3930</v>
       </c>
-      <c r="AW19" s="3">
+      <c r="BD19" s="3">
         <v>3907</v>
       </c>
-      <c r="AX19" s="3">
+      <c r="BE19" s="3">
         <v>4082</v>
+      </c>
+      <c r="BF19" s="1">
+        <v>4032</v>
       </c>
     </row>
   </sheetData>

--- a/PARTNER PERFORMANCE.xlsx
+++ b/PARTNER PERFORMANCE.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
   <si>
     <t>BENGKAYANG|BENGKAYANG</t>
   </si>
@@ -246,6 +246,30 @@
   </si>
   <si>
     <t>VLR_SUBS JULI</t>
+  </si>
+  <si>
+    <t>Prepaid Rev AGUSTUS</t>
+  </si>
+  <si>
+    <t>Primary Agustus</t>
+  </si>
+  <si>
+    <t>RGUGA FWA ALL CHANNEL AGUSTUS</t>
+  </si>
+  <si>
+    <t>RGUGA-Trad AGUSTUS</t>
+  </si>
+  <si>
+    <t>Secondary AGUSTUS</t>
+  </si>
+  <si>
+    <t>Tertiary B# AGUSTUS</t>
+  </si>
+  <si>
+    <t>Trade Supply AGUSTUS</t>
+  </si>
+  <si>
+    <t>VLR_SUBS AGUSTUS</t>
   </si>
 </sst>
 </file>
@@ -614,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:BF19"/>
+  <dimension ref="A5:BN19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36.90625" style="1" bestFit="1" customWidth="1"/>
@@ -626,58 +650,62 @@
     <col min="7" max="7" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.7265625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7265625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="32.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="31.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="29.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="28.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.7265625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="20.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17" style="1" customWidth="1"/>
-    <col min="31" max="31" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15" style="1" customWidth="1"/>
-    <col min="38" max="38" width="18.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="19.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="15.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="15.36328125" style="1" customWidth="1"/>
-    <col min="45" max="45" width="20.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="18.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="16.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="17.26953125" style="1" customWidth="1"/>
-    <col min="52" max="52" width="18.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="16.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="15.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="14.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="16384" width="8.7265625" style="1"/>
+    <col min="10" max="10" width="20.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="12.7265625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="32.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="33.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="31.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="29.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="28.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="28.7265625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="20.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="21.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17" style="1" customWidth="1"/>
+    <col min="34" max="34" width="21.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="17.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="15" style="1" customWidth="1"/>
+    <col min="43" max="43" width="18.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="14.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="50" width="15.36328125" style="1" customWidth="1"/>
+    <col min="51" max="51" width="20.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="18.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="16.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="58" width="17.26953125" style="1" customWidth="1"/>
+    <col min="59" max="59" width="18.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="19.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="16.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="15.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="14.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="18.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="67" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
@@ -705,155 +733,179 @@
       <c r="I5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="N5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="O5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="P5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="Q5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="R5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="S5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="T5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="U5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="V5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="W5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="X5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="Y5" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="Z5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="AB5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Z5" s="4" t="s">
+      <c r="AC5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AA5" s="4" t="s">
+      <c r="AD5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AB5" s="4" t="s">
+      <c r="AE5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AC5" s="4" t="s">
+      <c r="AF5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AD5" s="4" t="s">
+      <c r="AG5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="AE5" s="4" t="s">
+      <c r="AH5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AF5" s="4" t="s">
+      <c r="AJ5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AG5" s="4" t="s">
+      <c r="AK5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="AH5" s="4" t="s">
+      <c r="AL5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AI5" s="4" t="s">
+      <c r="AM5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AJ5" s="4" t="s">
+      <c r="AN5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AK5" s="4" t="s">
+      <c r="AO5" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="AL5" s="4" t="s">
+      <c r="AP5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AQ5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM5" s="4" t="s">
+      <c r="AR5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AN5" s="4" t="s">
+      <c r="AS5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AO5" s="4" t="s">
+      <c r="AT5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="AP5" s="4" t="s">
+      <c r="AU5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AQ5" s="4" t="s">
+      <c r="AV5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AR5" s="4" t="s">
+      <c r="AW5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="AS5" s="4" t="s">
+      <c r="AX5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AY5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AT5" s="4" t="s">
+      <c r="AZ5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AU5" s="4" t="s">
+      <c r="BA5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AV5" s="4" t="s">
+      <c r="BB5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="AW5" s="4" t="s">
+      <c r="BC5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AX5" s="4" t="s">
+      <c r="BD5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AY5" s="4" t="s">
+      <c r="BE5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="AZ5" s="4" t="s">
+      <c r="BF5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="BG5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="BA5" s="4" t="s">
+      <c r="BH5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="BB5" s="4" t="s">
+      <c r="BI5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="BC5" s="4" t="s">
+      <c r="BJ5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="BD5" s="4" t="s">
+      <c r="BK5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BE5" s="4" t="s">
+      <c r="BL5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="BF5" s="4" t="s">
+      <c r="BM5" s="4" t="s">
         <v>73</v>
       </c>
+      <c r="BN5" s="4" t="s">
+        <v>81</v>
+      </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -882,154 +934,178 @@
         <v>510028495.30856544</v>
       </c>
       <c r="J6" s="3">
+        <v>515379129.96050423</v>
+      </c>
+      <c r="K6" s="3">
         <v>203513.51351351399</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>370990.99099099002</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>386307432.43243247</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>4336036.0360360341</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>2132439.6396396412</v>
       </c>
-      <c r="O6" s="3">
+      <c r="P6" s="3">
         <v>10829729.729729731</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <v>8936545.9459459446</v>
       </c>
-      <c r="Q6" s="3">
-        <v>0</v>
-      </c>
       <c r="R6" s="3">
-        <v>0</v>
+        <v>5206306.3063063044</v>
       </c>
       <c r="S6" s="3">
         <v>0</v>
       </c>
       <c r="T6" s="3">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3">
         <v>2</v>
       </c>
-      <c r="U6" s="3">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3">
+      <c r="W6" s="3">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3">
         <v>4</v>
       </c>
-      <c r="W6" s="3">
+      <c r="Y6" s="3">
         <v>2</v>
       </c>
-      <c r="X6" s="3">
+      <c r="Z6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="3">
         <v>119</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="AB6" s="3">
         <v>160</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="AC6" s="3">
         <v>403</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AD6" s="3">
         <v>532</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AE6" s="3">
         <v>415</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AF6" s="3">
         <v>552</v>
       </c>
-      <c r="AD6" s="3">
+      <c r="AG6" s="3">
         <v>488</v>
       </c>
-      <c r="AE6" s="3">
+      <c r="AH6" s="3">
+        <v>534</v>
+      </c>
+      <c r="AI6" s="3">
         <v>35808378.378378376</v>
       </c>
-      <c r="AF6" s="3">
+      <c r="AJ6" s="3">
         <v>39277297.297297299</v>
       </c>
-      <c r="AG6" s="3">
+      <c r="AK6" s="3">
         <v>482659423.42342341</v>
       </c>
-      <c r="AH6" s="3">
+      <c r="AL6" s="3">
         <v>49057567.567567565</v>
       </c>
-      <c r="AI6" s="3">
+      <c r="AM6" s="3">
         <v>75839196.396396399</v>
       </c>
-      <c r="AJ6" s="3">
+      <c r="AN6" s="3">
         <v>93100225.225225225</v>
       </c>
-      <c r="AK6" s="3">
+      <c r="AO6" s="3">
         <v>204066018.01801801</v>
       </c>
-      <c r="AL6" s="3">
+      <c r="AP6" s="3">
+        <v>62274684.684684679</v>
+      </c>
+      <c r="AQ6" s="3">
         <v>252829513.51351351</v>
       </c>
-      <c r="AM6" s="3">
+      <c r="AR6" s="3">
         <v>242080702.7027027</v>
       </c>
-      <c r="AN6" s="3">
+      <c r="AS6" s="3">
         <v>277503809.009009</v>
       </c>
-      <c r="AO6" s="3">
+      <c r="AT6" s="3">
         <v>270568565.76576579</v>
       </c>
-      <c r="AP6" s="3">
+      <c r="AU6" s="3">
         <v>269897936.93693691</v>
       </c>
-      <c r="AQ6" s="3">
+      <c r="AV6" s="3">
         <v>239724342.34234235</v>
       </c>
-      <c r="AR6" s="3">
+      <c r="AW6" s="3">
         <v>251169441.44144145</v>
       </c>
-      <c r="AS6" s="3">
+      <c r="AX6" s="3">
+        <v>245843405.4054054</v>
+      </c>
+      <c r="AY6" s="3">
         <v>38450680.180180185</v>
       </c>
-      <c r="AT6" s="3">
+      <c r="AZ6" s="3">
         <v>39688783.783783786</v>
       </c>
-      <c r="AU6" s="3">
+      <c r="BA6" s="3">
         <v>485471396.3963964</v>
       </c>
-      <c r="AV6" s="3">
+      <c r="BB6" s="3">
         <v>49136666.666666664</v>
       </c>
-      <c r="AW6" s="3">
+      <c r="BC6" s="3">
         <v>81013693.693693697</v>
       </c>
-      <c r="AX6" s="3">
+      <c r="BD6" s="3">
         <v>89537522.522522524</v>
       </c>
-      <c r="AY6" s="3">
+      <c r="BE6" s="3">
         <v>205267567.56756756</v>
       </c>
-      <c r="AZ6" s="3">
+      <c r="BF6" s="3">
+        <v>58132522.522522517</v>
+      </c>
+      <c r="BG6" s="3">
         <v>8040</v>
       </c>
-      <c r="BA6" s="3">
+      <c r="BH6" s="3">
         <v>8268</v>
       </c>
-      <c r="BB6" s="3">
+      <c r="BI6" s="3">
         <v>8133</v>
       </c>
-      <c r="BC6" s="3">
+      <c r="BJ6" s="3">
         <v>8485</v>
       </c>
-      <c r="BD6" s="3">
+      <c r="BK6" s="3">
         <v>10848</v>
       </c>
-      <c r="BE6" s="3">
+      <c r="BL6" s="3">
         <v>7931</v>
       </c>
-      <c r="BF6" s="1">
+      <c r="BM6" s="3">
         <v>7724</v>
       </c>
+      <c r="BN6" s="3">
+        <v>9583</v>
+      </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
@@ -1058,31 +1134,31 @@
         <v>34312438.506123811</v>
       </c>
       <c r="J7" s="3">
-        <v>0</v>
+        <v>52696692.954297103</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
       </c>
       <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
         <v>713513.51351351396</v>
       </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
       <c r="N7" s="3">
         <v>0</v>
       </c>
       <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
         <v>59459.459459459998</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <v>644144.14414414403</v>
       </c>
-      <c r="Q7" s="3">
-        <v>0</v>
-      </c>
       <c r="R7" s="3">
-        <v>0</v>
+        <v>315809146.84684682</v>
       </c>
       <c r="S7" s="3">
         <v>0</v>
@@ -1100,112 +1176,136 @@
         <v>0</v>
       </c>
       <c r="X7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3">
         <v>6</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="AB7" s="3">
         <v>3</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="AC7" s="3">
         <v>13</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AD7" s="3">
         <v>5</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AE7" s="3">
         <v>7</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AF7" s="3">
         <v>8</v>
       </c>
-      <c r="AD7" s="3">
+      <c r="AG7" s="3">
         <v>4</v>
       </c>
-      <c r="AE7" s="3">
+      <c r="AH7" s="3">
+        <v>9</v>
+      </c>
+      <c r="AI7" s="3">
         <v>453153.15315315302</v>
       </c>
-      <c r="AF7" s="3">
+      <c r="AJ7" s="3">
         <v>176576.576576577</v>
       </c>
-      <c r="AG7" s="3">
+      <c r="AK7" s="3">
         <v>794594.59459459502</v>
       </c>
-      <c r="AH7" s="3">
+      <c r="AL7" s="3">
         <v>216216.21621621601</v>
       </c>
-      <c r="AI7" s="3">
+      <c r="AM7" s="3">
         <v>2323423.4234234239</v>
       </c>
-      <c r="AJ7" s="3">
+      <c r="AN7" s="3">
         <v>2081981.981981982</v>
       </c>
-      <c r="AK7" s="3">
+      <c r="AO7" s="3">
         <v>12310810.81081081</v>
       </c>
-      <c r="AL7" s="3">
+      <c r="AP7" s="3">
+        <v>49355855.855855852</v>
+      </c>
+      <c r="AQ7" s="3">
         <v>39438864.864864863</v>
       </c>
-      <c r="AM7" s="3">
+      <c r="AR7" s="3">
         <v>40892414.414414413</v>
       </c>
-      <c r="AN7" s="3">
+      <c r="AS7" s="3">
         <v>38603315.315315314</v>
       </c>
-      <c r="AO7" s="3">
+      <c r="AT7" s="3">
         <v>36530513.513513513</v>
       </c>
-      <c r="AP7" s="3">
+      <c r="AU7" s="3">
         <v>41422684.684684686</v>
       </c>
-      <c r="AQ7" s="3">
+      <c r="AV7" s="3">
         <v>35097585.585585587</v>
       </c>
-      <c r="AR7" s="3">
+      <c r="AW7" s="3">
         <v>21179207.207207207</v>
       </c>
-      <c r="AS7" s="3">
+      <c r="AX7" s="3">
+        <v>29349477.477477476</v>
+      </c>
+      <c r="AY7" s="3">
         <v>469369.36936936999</v>
       </c>
-      <c r="AT7" s="3">
+      <c r="AZ7" s="3">
         <v>24799009.009009007</v>
       </c>
-      <c r="AU7" s="3">
+      <c r="BA7" s="3">
         <v>794594.59459459502</v>
       </c>
-      <c r="AV7" s="3">
+      <c r="BB7" s="3">
         <v>216216.21621621601</v>
       </c>
-      <c r="AW7" s="3">
+      <c r="BC7" s="3">
         <v>2323423.4234234239</v>
       </c>
-      <c r="AX7" s="3">
+      <c r="BD7" s="3">
         <v>1982882.8828828831</v>
       </c>
-      <c r="AY7" s="3">
+      <c r="BE7" s="3">
         <v>11959009.009009007</v>
       </c>
-      <c r="AZ7" s="3">
+      <c r="BF7" s="3">
+        <v>6763063.0630630637</v>
+      </c>
+      <c r="BG7" s="3">
         <v>1216</v>
       </c>
-      <c r="BA7" s="3">
+      <c r="BH7" s="3">
         <v>1049</v>
       </c>
-      <c r="BB7" s="3">
+      <c r="BI7" s="3">
         <v>1148</v>
       </c>
-      <c r="BC7" s="3">
+      <c r="BJ7" s="3">
         <v>1120</v>
       </c>
-      <c r="BD7" s="3">
+      <c r="BK7" s="3">
         <v>1095</v>
       </c>
-      <c r="BE7" s="3">
+      <c r="BL7" s="3">
         <v>1110</v>
       </c>
-      <c r="BF7" s="1">
+      <c r="BM7" s="3">
         <v>1527</v>
       </c>
+      <c r="BN7" s="3">
+        <v>1333</v>
+      </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
@@ -1234,154 +1334,178 @@
         <v>339951384.80923343</v>
       </c>
       <c r="J8" s="3">
+        <v>388078336.9102633</v>
+      </c>
+      <c r="K8" s="3">
         <v>102837.837837838</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1244009.009009009</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1299946578.3783784</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1014535388.2882882</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1663963.963963965</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4584684.6846846826</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5087768.4684684696</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
+        <v>5709684.6846846854</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>5</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>1</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
         <v>65</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AB8" s="3">
         <v>35</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AC8" s="3">
         <v>83</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AD8" s="3">
         <v>56</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AE8" s="3">
         <v>9</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AF8" s="3">
         <v>31</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AG8" s="3">
         <v>71</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AH8" s="3">
+        <v>70</v>
+      </c>
+      <c r="AI8" s="3">
         <v>140672657.65765765</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AJ8" s="3">
         <v>55676666.666666672</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AK8" s="3">
         <v>343935509.009009</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AL8" s="3">
         <v>456286036.03603601</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AM8" s="3">
         <v>95671171.171171173</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AN8" s="3">
         <v>90238843.243243247</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AO8" s="3">
         <v>103439091.89189188</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AP8" s="3">
+        <v>72676576.576576576</v>
+      </c>
+      <c r="AQ8" s="3">
         <v>111718427.92792793</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AR8" s="3">
         <v>101496851.35135135</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AS8" s="3">
         <v>107538207.2072072</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AT8" s="3">
         <v>107522270.27027027</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AU8" s="3">
         <v>100889360.36036035</v>
       </c>
-      <c r="AQ8" s="3">
+      <c r="AV8" s="3">
         <v>108237441.44144145</v>
       </c>
-      <c r="AR8" s="3">
+      <c r="AW8" s="3">
         <v>97111315.315315306</v>
       </c>
-      <c r="AS8" s="3">
+      <c r="AX8" s="3">
+        <v>105140567.56756757</v>
+      </c>
+      <c r="AY8" s="3">
         <v>135877229.72972974</v>
       </c>
-      <c r="AT8" s="3">
+      <c r="AZ8" s="3">
         <v>51686918.918918923</v>
       </c>
-      <c r="AU8" s="3">
+      <c r="BA8" s="3">
         <v>158870405.4054054</v>
       </c>
-      <c r="AV8" s="3">
+      <c r="BB8" s="3">
         <v>201043468.46846849</v>
       </c>
-      <c r="AW8" s="3">
+      <c r="BC8" s="3">
         <v>92234324.324324325</v>
       </c>
-      <c r="AX8" s="3">
+      <c r="BD8" s="3">
         <v>86003513.51351352</v>
       </c>
-      <c r="AY8" s="3">
+      <c r="BE8" s="3">
         <v>99631081.081081077</v>
       </c>
-      <c r="AZ8" s="3">
+      <c r="BF8" s="3">
+        <v>67764144.144144148</v>
+      </c>
+      <c r="BG8" s="3">
         <v>3688</v>
       </c>
-      <c r="BA8" s="3">
+      <c r="BH8" s="3">
         <v>3602</v>
       </c>
-      <c r="BB8" s="3">
+      <c r="BI8" s="3">
         <v>3462</v>
       </c>
-      <c r="BC8" s="3">
+      <c r="BJ8" s="3">
         <v>3640</v>
       </c>
-      <c r="BD8" s="3">
+      <c r="BK8" s="3">
         <v>3775</v>
       </c>
-      <c r="BE8" s="3">
+      <c r="BL8" s="3">
         <v>2027</v>
       </c>
-      <c r="BF8" s="1">
+      <c r="BM8" s="3">
         <v>3579</v>
       </c>
+      <c r="BN8" s="3">
+        <v>3885</v>
+      </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1410,37 +1534,37 @@
         <v>218776646.67133695</v>
       </c>
       <c r="J9" s="3">
+        <v>230489931.78063968</v>
+      </c>
+      <c r="K9" s="3">
         <v>588963.96396396297</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>117927.927927928</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>832432.43243243301</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12427027.027027024</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13372972.972972976</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2354954.9549549548</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7701126.1261261273</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
       <c r="R9" s="3">
-        <v>0</v>
+        <v>380433333.33333331</v>
       </c>
       <c r="S9" s="3">
         <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" s="3">
         <v>0</v>
@@ -1449,115 +1573,139 @@
         <v>1</v>
       </c>
       <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="3">
         <v>4</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="3">
         <v>28</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AB9" s="3">
         <v>108</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AC9" s="3">
         <v>41</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AD9" s="3">
         <v>16</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AE9" s="3">
         <v>65</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AF9" s="3">
         <v>48</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AG9" s="3">
         <v>46</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AH9" s="3">
+        <v>26</v>
+      </c>
+      <c r="AI9" s="3">
         <v>16853738.738738734</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AJ9" s="3">
         <v>14597882.882882884</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AK9" s="3">
         <v>19118198.198198199</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AL9" s="3">
         <v>32209279.27927928</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AM9" s="3">
         <v>67755180.180180177</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AN9" s="3">
         <v>118357882.88288288</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AO9" s="3">
         <v>104305630.63063063</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AP9" s="3">
+        <v>68358558.558558553</v>
+      </c>
+      <c r="AQ9" s="3">
         <v>84993513.51351352</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AR9" s="3">
         <v>85767216.216216207</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AS9" s="3">
         <v>86059351.351351365</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AT9" s="3">
         <v>87400207.207207203</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AU9" s="3">
         <v>82731792.792792797</v>
       </c>
-      <c r="AQ9" s="3">
+      <c r="AV9" s="3">
         <v>82382234.234234244</v>
       </c>
-      <c r="AR9" s="3">
+      <c r="AW9" s="3">
         <v>80699774.774774775</v>
       </c>
-      <c r="AS9" s="3">
+      <c r="AX9" s="3">
+        <v>81162324.324324325</v>
+      </c>
+      <c r="AY9" s="3">
         <v>16066576.576576576</v>
       </c>
-      <c r="AT9" s="3">
+      <c r="AZ9" s="3">
         <v>15452072.072072072</v>
       </c>
-      <c r="AU9" s="3">
+      <c r="BA9" s="3">
         <v>19869324.324324325</v>
       </c>
-      <c r="AV9" s="3">
+      <c r="BB9" s="3">
         <v>31971441.441441439</v>
       </c>
-      <c r="AW9" s="3">
+      <c r="BC9" s="3">
         <v>68640405.405405402</v>
       </c>
-      <c r="AX9" s="3">
+      <c r="BD9" s="3">
         <v>116400675.67567568</v>
       </c>
-      <c r="AY9" s="3">
+      <c r="BE9" s="3">
         <v>96526801.801801801</v>
       </c>
-      <c r="AZ9" s="3">
+      <c r="BF9" s="3">
+        <v>42807297.297297299</v>
+      </c>
+      <c r="BG9" s="3">
         <v>3479</v>
       </c>
-      <c r="BA9" s="3">
+      <c r="BH9" s="3">
         <v>3353</v>
       </c>
-      <c r="BB9" s="3">
+      <c r="BI9" s="3">
         <v>3503</v>
       </c>
-      <c r="BC9" s="3">
+      <c r="BJ9" s="3">
         <v>3534</v>
       </c>
-      <c r="BD9" s="3">
+      <c r="BK9" s="3">
         <v>3237</v>
       </c>
-      <c r="BE9" s="3">
+      <c r="BL9" s="3">
         <v>3593</v>
       </c>
-      <c r="BF9" s="1">
+      <c r="BM9" s="3">
         <v>3552</v>
       </c>
+      <c r="BN9" s="3">
+        <v>4264</v>
+      </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1586,31 +1734,31 @@
         <v>247513395.90166593</v>
       </c>
       <c r="J10" s="3">
+        <v>244639196.17200372</v>
+      </c>
+      <c r="K10" s="3">
         <v>206576.576576577</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>996306.30630630802</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>457257432.43243247</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1063714864.8648649</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5381981.9819819806</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1900000.0000000009</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>265765.76576576597</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>1389189.1891891891</v>
       </c>
       <c r="S10" s="3">
         <v>0</v>
@@ -1622,118 +1770,142 @@
         <v>0</v>
       </c>
       <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
         <v>1</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="3">
         <v>40</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AB10" s="3">
         <v>63</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AC10" s="3">
         <v>97</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AD10" s="3">
         <v>36</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AE10" s="3">
         <v>25</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AF10" s="3">
         <v>57</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AG10" s="3">
         <v>28</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AH10" s="3">
+        <v>43</v>
+      </c>
+      <c r="AI10" s="3">
         <v>16446936.936936937</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AJ10" s="3">
         <v>17774864.864864867</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AK10" s="3">
         <v>21434909.909909911</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AL10" s="3">
         <v>26308468.468468469</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AM10" s="3">
         <v>27991216.216216218</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AN10" s="3">
         <v>27848198.198198196</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AO10" s="3">
         <v>41664639.639639638</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AP10" s="3">
+        <v>15765765.765765764</v>
+      </c>
+      <c r="AQ10" s="3">
         <v>113496135.13513513</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AR10" s="3">
         <v>113179279.27927928</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AS10" s="3">
         <v>119714324.32432432</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AT10" s="3">
         <v>112842799.0990991</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AU10" s="3">
         <v>112275783.78378379</v>
       </c>
-      <c r="AQ10" s="3">
+      <c r="AV10" s="3">
         <v>108577927.92792793</v>
       </c>
-      <c r="AR10" s="3">
+      <c r="AW10" s="3">
         <v>104389837.83783785</v>
       </c>
-      <c r="AS10" s="3">
+      <c r="AX10" s="3">
+        <v>103704540.54054055</v>
+      </c>
+      <c r="AY10" s="3">
         <v>15685315.315315315</v>
       </c>
-      <c r="AT10" s="3">
+      <c r="AZ10" s="3">
         <v>16278648.648648648</v>
       </c>
-      <c r="AU10" s="3">
+      <c r="BA10" s="3">
         <v>18936576.576576576</v>
       </c>
-      <c r="AV10" s="3">
+      <c r="BB10" s="3">
         <v>19900180.180180181</v>
       </c>
-      <c r="AW10" s="3">
+      <c r="BC10" s="3">
         <v>26888513.513513513</v>
       </c>
-      <c r="AX10" s="3">
+      <c r="BD10" s="3">
         <v>26167837.837837838</v>
       </c>
-      <c r="AY10" s="3">
+      <c r="BE10" s="3">
         <v>40067882.882882878</v>
       </c>
-      <c r="AZ10" s="3">
+      <c r="BF10" s="3">
+        <v>15138288.288288288</v>
+      </c>
+      <c r="BG10" s="3">
         <v>2881</v>
       </c>
-      <c r="BA10" s="3">
+      <c r="BH10" s="3">
         <v>2710</v>
       </c>
-      <c r="BB10" s="3">
+      <c r="BI10" s="3">
         <v>2948</v>
       </c>
-      <c r="BC10" s="3">
+      <c r="BJ10" s="3">
         <v>2985</v>
       </c>
-      <c r="BD10" s="3">
+      <c r="BK10" s="3">
         <v>2573</v>
       </c>
-      <c r="BE10" s="3">
+      <c r="BL10" s="3">
         <v>3004</v>
       </c>
-      <c r="BF10" s="1">
+      <c r="BM10" s="3">
         <v>3081</v>
       </c>
+      <c r="BN10" s="3">
+        <v>3253</v>
+      </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -1762,154 +1934,178 @@
         <v>845331062.05816829</v>
       </c>
       <c r="J11" s="3">
+        <v>895962005.21395588</v>
+      </c>
+      <c r="K11" s="3">
         <v>638506009.90990984</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="3">
         <v>822941764.86486495</v>
       </c>
-      <c r="L11" s="3">
+      <c r="M11" s="3">
         <v>638930528.82882881</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>548376944.14414418</v>
       </c>
-      <c r="N11" s="3">
+      <c r="O11" s="3">
         <v>4736872.9729729686</v>
       </c>
-      <c r="O11" s="3">
+      <c r="P11" s="3">
         <v>42265579.279279277</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>44588547.747747749</v>
       </c>
-      <c r="Q11" s="3">
-        <v>0</v>
-      </c>
       <c r="R11" s="3">
+        <v>11081555.855855862</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3">
         <v>3</v>
       </c>
-      <c r="S11" s="3">
-        <v>0</v>
-      </c>
-      <c r="T11" s="3">
+      <c r="U11" s="3">
+        <v>0</v>
+      </c>
+      <c r="V11" s="3">
         <v>2</v>
       </c>
-      <c r="U11" s="3">
-        <v>0</v>
-      </c>
-      <c r="V11" s="3">
+      <c r="W11" s="3">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3">
         <v>9</v>
       </c>
-      <c r="W11" s="3">
+      <c r="Y11" s="3">
         <v>2</v>
       </c>
-      <c r="X11" s="3">
+      <c r="Z11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="3">
         <v>517</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="AB11" s="3">
         <v>478</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="AC11" s="3">
         <v>1197</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AD11" s="3">
         <v>1029</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AE11" s="3">
         <v>666</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AF11" s="3">
         <v>913</v>
       </c>
-      <c r="AD11" s="3">
+      <c r="AG11" s="3">
         <v>1436</v>
       </c>
-      <c r="AE11" s="3">
+      <c r="AH11" s="3">
+        <v>1045</v>
+      </c>
+      <c r="AI11" s="3">
         <v>670162702.70270276</v>
       </c>
-      <c r="AF11" s="3">
+      <c r="AJ11" s="3">
         <v>679806493.69369364</v>
       </c>
-      <c r="AG11" s="3">
+      <c r="AK11" s="3">
         <v>604098193.69369364</v>
       </c>
-      <c r="AH11" s="3">
+      <c r="AL11" s="3">
         <v>598366390.990991</v>
       </c>
-      <c r="AI11" s="3">
+      <c r="AM11" s="3">
         <v>604745206.30630636</v>
       </c>
-      <c r="AJ11" s="3">
+      <c r="AN11" s="3">
         <v>434344633.33333331</v>
       </c>
-      <c r="AK11" s="3">
+      <c r="AO11" s="3">
         <v>625995597.29729724</v>
       </c>
-      <c r="AL11" s="3">
+      <c r="AP11" s="3">
+        <v>371748318.91891891</v>
+      </c>
+      <c r="AQ11" s="3">
         <v>648350765.76576579</v>
       </c>
-      <c r="AM11" s="3">
+      <c r="AR11" s="3">
         <v>662175596.84684682</v>
       </c>
-      <c r="AN11" s="3">
+      <c r="AS11" s="3">
         <v>702347079.27927923</v>
       </c>
-      <c r="AO11" s="3">
+      <c r="AT11" s="3">
         <v>608951778.37837839</v>
       </c>
-      <c r="AP11" s="3">
+      <c r="AU11" s="3">
         <v>631184342.34234238</v>
       </c>
-      <c r="AQ11" s="3">
+      <c r="AV11" s="3">
         <v>602764971.17117119</v>
       </c>
-      <c r="AR11" s="3">
+      <c r="AW11" s="3">
         <v>579324936.93693697</v>
       </c>
-      <c r="AS11" s="3">
+      <c r="AX11" s="3">
+        <v>602885882.88288295</v>
+      </c>
+      <c r="AY11" s="3">
         <v>586018468.46846843</v>
       </c>
-      <c r="AT11" s="3">
+      <c r="AZ11" s="3">
         <v>627651666.66666663</v>
       </c>
-      <c r="AU11" s="3">
+      <c r="BA11" s="3">
         <v>507988153.15315318</v>
       </c>
-      <c r="AV11" s="3">
+      <c r="BB11" s="3">
         <v>491883333.33333331</v>
       </c>
-      <c r="AW11" s="3">
+      <c r="BC11" s="3">
         <v>545409414.41441441</v>
       </c>
-      <c r="AX11" s="3">
+      <c r="BD11" s="3">
         <v>403078783.78378379</v>
       </c>
-      <c r="AY11" s="3">
+      <c r="BE11" s="3">
         <v>594881711.71171176</v>
       </c>
-      <c r="AZ11" s="3">
+      <c r="BF11" s="3">
+        <v>334078468.46846849</v>
+      </c>
+      <c r="BG11" s="3">
         <v>12944</v>
       </c>
-      <c r="BA11" s="3">
+      <c r="BH11" s="3">
         <v>13539</v>
       </c>
-      <c r="BB11" s="3">
+      <c r="BI11" s="3">
         <v>13340</v>
       </c>
-      <c r="BC11" s="3">
+      <c r="BJ11" s="3">
         <v>13326</v>
       </c>
-      <c r="BD11" s="3">
+      <c r="BK11" s="3">
         <v>12671</v>
       </c>
-      <c r="BE11" s="3">
+      <c r="BL11" s="3">
         <v>13401</v>
       </c>
-      <c r="BF11" s="1">
+      <c r="BM11" s="3">
         <v>13750</v>
       </c>
+      <c r="BN11" s="3">
+        <v>14382</v>
+      </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
@@ -1938,31 +2134,31 @@
         <v>201546534.46167859</v>
       </c>
       <c r="J12" s="3">
+        <v>206892343.33871564</v>
+      </c>
+      <c r="K12" s="3">
         <v>85090.090090088997</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>38513.513513514001</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9459.4594594589998</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5717117.1171171153</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>103305405.4054054</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>283000900.9009009</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>396291828.82882881</v>
       </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
       <c r="R12" s="3">
-        <v>0</v>
+        <v>530630.63063063298</v>
       </c>
       <c r="S12" s="3">
         <v>0</v>
@@ -1980,112 +2176,136 @@
         <v>0</v>
       </c>
       <c r="X12" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="3">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="AA12" s="3">
         <v>42</v>
       </c>
       <c r="AB12" s="3">
+        <v>229</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>68</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>42</v>
+      </c>
+      <c r="AE12" s="3">
         <v>57</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AF12" s="3">
         <v>31</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AG12" s="3">
         <v>68</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AH12" s="3">
+        <v>84</v>
+      </c>
+      <c r="AI12" s="3">
         <v>34624189.189189196</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AJ12" s="3">
         <v>28234009.009009007</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AK12" s="3">
         <v>23812612.612612613</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AL12" s="3">
         <v>35304504.504504502</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AM12" s="3">
         <v>49787387.387387387</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AN12" s="3">
         <v>47238288.288288288</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AO12" s="3">
         <v>111109459.45945945</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AP12" s="3">
+        <v>38942792.79279279</v>
+      </c>
+      <c r="AQ12" s="3">
         <v>141530813.51351351</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AR12" s="3">
         <v>147375786.03603604</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AS12" s="3">
         <v>156720349.54954955</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AT12" s="3">
         <v>146406531.53153151</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AU12" s="3">
         <v>159118252.25225225</v>
       </c>
-      <c r="AQ12" s="3">
+      <c r="AV12" s="3">
         <v>141919810.8108108</v>
       </c>
-      <c r="AR12" s="3">
+      <c r="AW12" s="3">
         <v>135319693.6936937</v>
       </c>
-      <c r="AS12" s="3">
+      <c r="AX12" s="3">
+        <v>143190450.45045045</v>
+      </c>
+      <c r="AY12" s="3">
         <v>28677585.585585583</v>
       </c>
-      <c r="AT12" s="3">
+      <c r="AZ12" s="3">
         <v>22354144.144144148</v>
       </c>
-      <c r="AU12" s="3">
+      <c r="BA12" s="3">
         <v>23202252.252252251</v>
       </c>
-      <c r="AV12" s="3">
+      <c r="BB12" s="3">
         <v>32816126.126126129</v>
       </c>
-      <c r="AW12" s="3">
+      <c r="BC12" s="3">
         <v>19275135.135135133</v>
       </c>
-      <c r="AX12" s="3">
+      <c r="BD12" s="3">
         <v>45052972.972972974</v>
       </c>
-      <c r="AY12" s="3">
+      <c r="BE12" s="3">
         <v>69285585.585585579</v>
       </c>
-      <c r="AZ12" s="3">
+      <c r="BF12" s="3">
+        <v>38376756.756756753</v>
+      </c>
+      <c r="BG12" s="3">
         <v>4845</v>
       </c>
-      <c r="BA12" s="3">
+      <c r="BH12" s="3">
         <v>4158</v>
       </c>
-      <c r="BB12" s="3">
+      <c r="BI12" s="3">
         <v>4484</v>
       </c>
-      <c r="BC12" s="3">
+      <c r="BJ12" s="3">
         <v>4541</v>
       </c>
-      <c r="BD12" s="3">
+      <c r="BK12" s="3">
         <v>4630</v>
       </c>
-      <c r="BE12" s="3">
+      <c r="BL12" s="3">
         <v>4632</v>
       </c>
-      <c r="BF12" s="1">
+      <c r="BM12" s="3">
         <v>4824</v>
       </c>
+      <c r="BN12" s="3">
+        <v>5614</v>
+      </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -2114,154 +2334,178 @@
         <v>287413587.27569234</v>
       </c>
       <c r="J13" s="3">
+        <v>295519764.03191042</v>
+      </c>
+      <c r="K13" s="3">
         <v>3317500</v>
       </c>
-      <c r="K13" s="3">
+      <c r="L13" s="3">
         <v>4828963.9639639622</v>
       </c>
-      <c r="L13" s="3">
+      <c r="M13" s="3">
         <v>3683333.333333333</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <v>1741441.441441441</v>
       </c>
-      <c r="N13" s="3">
+      <c r="O13" s="3">
         <v>5082882.8828828828</v>
       </c>
-      <c r="O13" s="3">
+      <c r="P13" s="3">
         <v>5099099.0990990978</v>
       </c>
-      <c r="P13" s="3">
+      <c r="Q13" s="3">
         <v>6724681.9819819843</v>
       </c>
-      <c r="Q13" s="3">
-        <v>0</v>
-      </c>
       <c r="R13" s="3">
+        <v>6419819.8198198183</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
         <v>5</v>
       </c>
-      <c r="S13" s="3">
-        <v>0</v>
-      </c>
-      <c r="T13" s="3">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
         <v>1</v>
       </c>
-      <c r="U13" s="3">
-        <v>0</v>
-      </c>
-      <c r="V13" s="3">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
         <v>2</v>
       </c>
-      <c r="W13" s="3">
-        <v>0</v>
-      </c>
-      <c r="X13" s="3">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
         <v>73</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="AB13" s="3">
         <v>127</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="AC13" s="3">
         <v>121</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="AD13" s="3">
         <v>65</v>
       </c>
-      <c r="AB13" s="3">
+      <c r="AE13" s="3">
         <v>15</v>
       </c>
-      <c r="AC13" s="3">
+      <c r="AF13" s="3">
         <v>59</v>
       </c>
-      <c r="AD13" s="3">
+      <c r="AG13" s="3">
         <v>63</v>
       </c>
-      <c r="AE13" s="3">
+      <c r="AH13" s="3">
+        <v>36</v>
+      </c>
+      <c r="AI13" s="3">
         <v>51839121.621621624</v>
       </c>
-      <c r="AF13" s="3">
+      <c r="AJ13" s="3">
         <v>62088198.198198199</v>
       </c>
-      <c r="AG13" s="3">
+      <c r="AK13" s="3">
         <v>71674324.324324325</v>
       </c>
-      <c r="AH13" s="3">
+      <c r="AL13" s="3">
         <v>76762612.612612605</v>
       </c>
-      <c r="AI13" s="3">
+      <c r="AM13" s="3">
         <v>55213513.513513513</v>
       </c>
-      <c r="AJ13" s="3">
+      <c r="AN13" s="3">
         <v>55615315.315315314</v>
       </c>
-      <c r="AK13" s="3">
+      <c r="AO13" s="3">
         <v>53050210.810810819</v>
       </c>
-      <c r="AL13" s="3">
+      <c r="AP13" s="3">
+        <v>49063063.063063063</v>
+      </c>
+      <c r="AQ13" s="3">
         <v>89223153.153153151</v>
       </c>
-      <c r="AM13" s="3">
+      <c r="AR13" s="3">
         <v>87350851.351351351</v>
       </c>
-      <c r="AN13" s="3">
+      <c r="AS13" s="3">
         <v>96104349.54954955</v>
       </c>
-      <c r="AO13" s="3">
+      <c r="AT13" s="3">
         <v>88084173.873873875</v>
       </c>
-      <c r="AP13" s="3">
+      <c r="AU13" s="3">
         <v>86464783.783783779</v>
       </c>
-      <c r="AQ13" s="3">
+      <c r="AV13" s="3">
         <v>88053180.180180177</v>
       </c>
-      <c r="AR13" s="3">
+      <c r="AW13" s="3">
         <v>86734216.216216221</v>
       </c>
-      <c r="AS13" s="3">
+      <c r="AX13" s="3">
+        <v>87199500</v>
+      </c>
+      <c r="AY13" s="3">
         <v>48542576.576576576</v>
       </c>
-      <c r="AT13" s="3">
+      <c r="AZ13" s="3">
         <v>53949738.738738738</v>
       </c>
-      <c r="AU13" s="3">
+      <c r="BA13" s="3">
         <v>71818783.783783779</v>
       </c>
-      <c r="AV13" s="3">
+      <c r="BB13" s="3">
         <v>77257333.333333328</v>
       </c>
-      <c r="AW13" s="3">
+      <c r="BC13" s="3">
         <v>50835405.40540541</v>
       </c>
-      <c r="AX13" s="3">
+      <c r="BD13" s="3">
         <v>51781351.351351351</v>
       </c>
-      <c r="AY13" s="3">
+      <c r="BE13" s="3">
         <v>47952882.882882878</v>
       </c>
-      <c r="AZ13" s="3">
+      <c r="BF13" s="3">
+        <v>43423243.24324324</v>
+      </c>
+      <c r="BG13" s="3">
         <v>3583</v>
       </c>
-      <c r="BA13" s="3">
+      <c r="BH13" s="3">
         <v>3585</v>
       </c>
-      <c r="BB13" s="3">
+      <c r="BI13" s="3">
         <v>3730</v>
       </c>
-      <c r="BC13" s="3">
+      <c r="BJ13" s="3">
         <v>3698</v>
       </c>
-      <c r="BD13" s="3">
+      <c r="BK13" s="3">
         <v>3542</v>
       </c>
-      <c r="BE13" s="3">
+      <c r="BL13" s="3">
         <v>3662</v>
       </c>
-      <c r="BF13" s="1">
+      <c r="BM13" s="3">
         <v>3415</v>
       </c>
+      <c r="BN13" s="3">
+        <v>4160</v>
+      </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -2290,31 +2534,31 @@
         <v>533068956.22284913</v>
       </c>
       <c r="J14" s="3">
+        <v>563032350.55292141</v>
+      </c>
+      <c r="K14" s="3">
         <v>1043978150.4504504</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>811331229.72972977</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>18636109.909909911</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12635188.288288288</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>651672918.01801801</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>504025608.1081081</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>17138469.369369369</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
-        <v>4</v>
+        <v>15408427.027027026</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -2326,118 +2570,142 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>4</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>1</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>1</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="3">
         <v>483</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AB14" s="3">
         <v>427</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AC14" s="3">
         <v>1177</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AD14" s="3">
         <v>1010</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AE14" s="3">
         <v>202</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AF14" s="3">
         <v>227</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AG14" s="3">
         <v>151</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AH14" s="3">
+        <v>106</v>
+      </c>
+      <c r="AI14" s="3">
         <v>773978333.33333337</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AJ14" s="3">
         <v>763466792.7927928</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AK14" s="3">
         <v>823364037.83783782</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AL14" s="3">
         <v>724311539.63963974</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AM14" s="3">
         <v>811996692.7927928</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AN14" s="3">
         <v>636634596.3963964</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AO14" s="3">
         <v>821123052.25225234</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AP14" s="3">
+        <v>791461212.61261261</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>205230034.23423424</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AR14" s="3">
         <v>198082139.63963965</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AS14" s="3">
         <v>235105216.21621624</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AT14" s="3">
         <v>208732621.62162164</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AU14" s="3">
         <v>200317034.23423424</v>
       </c>
-      <c r="AQ14" s="3">
+      <c r="AV14" s="3">
         <v>184902018.01801801</v>
       </c>
-      <c r="AR14" s="3">
+      <c r="AW14" s="3">
         <v>193444061.26126125</v>
       </c>
-      <c r="AS14" s="3">
+      <c r="AX14" s="3">
+        <v>202463612.61261261</v>
+      </c>
+      <c r="AY14" s="3">
         <v>660584265.76576579</v>
       </c>
-      <c r="AT14" s="3">
+      <c r="AZ14" s="3">
         <v>734348657.65765762</v>
       </c>
-      <c r="AU14" s="3">
+      <c r="BA14" s="3">
         <v>828830720.72072077</v>
       </c>
-      <c r="AV14" s="3">
+      <c r="BB14" s="3">
         <v>728851666.66666663</v>
       </c>
-      <c r="AW14" s="3">
+      <c r="BC14" s="3">
         <v>705261756.75675678</v>
       </c>
-      <c r="AX14" s="3">
+      <c r="BD14" s="3">
         <v>506043243.24324328</v>
       </c>
-      <c r="AY14" s="3">
+      <c r="BE14" s="3">
         <v>757542027.02702713</v>
       </c>
-      <c r="AZ14" s="3">
+      <c r="BF14" s="3">
+        <v>706172612.61261261</v>
+      </c>
+      <c r="BG14" s="3">
         <v>6875</v>
       </c>
-      <c r="BA14" s="3">
+      <c r="BH14" s="3">
         <v>6717</v>
       </c>
-      <c r="BB14" s="3">
+      <c r="BI14" s="3">
         <v>7141</v>
       </c>
-      <c r="BC14" s="3">
+      <c r="BJ14" s="3">
         <v>7116</v>
       </c>
-      <c r="BD14" s="3">
+      <c r="BK14" s="3">
         <v>7539</v>
       </c>
-      <c r="BE14" s="3">
+      <c r="BL14" s="3">
         <v>8252</v>
       </c>
-      <c r="BF14" s="1">
+      <c r="BM14" s="3">
         <v>7079</v>
       </c>
+      <c r="BN14" s="3">
+        <v>8388</v>
+      </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -2466,154 +2734,178 @@
         <v>229537143.34768772</v>
       </c>
       <c r="J15" s="3">
+        <v>237898247.34620002</v>
+      </c>
+      <c r="K15" s="3">
         <v>373558.55855855701</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>449189.18918918999</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>545270.27027026995</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3872072.072072072</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3884684.684684685</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1560360.3603603591</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>20268.468468469</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
         <v>1</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
         <v>2</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
       <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
         <v>1</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
         <v>185</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AB15" s="3">
         <v>142</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AC15" s="3">
         <v>271</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AD15" s="3">
         <v>207</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AE15" s="3">
         <v>12</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AF15" s="3">
         <v>14</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AG15" s="3">
         <v>30</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AH15" s="3">
+        <v>36</v>
+      </c>
+      <c r="AI15" s="3">
         <v>10691756.756756758</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AJ15" s="3">
         <v>18032747.747747749</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AK15" s="3">
         <v>9393468.4684684686</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AL15" s="3">
         <v>13405405.405405406</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AM15" s="3">
         <v>3209009.0090090092</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AN15" s="3">
         <v>22269819.819819819</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AO15" s="3">
         <v>21335.135135134999</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
         <v>160495459.45945945</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AR15" s="3">
         <v>159850909.90990993</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AS15" s="3">
         <v>172412645.04504505</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AT15" s="3">
         <v>159028324.32432431</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AU15" s="3">
         <v>149578126.12612611</v>
       </c>
-      <c r="AQ15" s="3">
+      <c r="AV15" s="3">
         <v>147227872.07207206</v>
       </c>
-      <c r="AR15" s="3">
+      <c r="AW15" s="3">
         <v>137361405.4054054</v>
       </c>
-      <c r="AS15" s="3">
+      <c r="AX15" s="3">
+        <v>142317223.42342341</v>
+      </c>
+      <c r="AY15" s="3">
         <v>9338828.8288288284</v>
       </c>
-      <c r="AT15" s="3">
+      <c r="AZ15" s="3">
         <v>18017027.02702703</v>
       </c>
-      <c r="AU15" s="3">
+      <c r="BA15" s="3">
         <v>9646396.3963963985</v>
       </c>
-      <c r="AV15" s="3">
+      <c r="BB15" s="3">
         <v>13452072.072072072</v>
       </c>
-      <c r="AW15" s="3">
+      <c r="BC15" s="3">
         <v>3309729.7297297302</v>
       </c>
-      <c r="AX15" s="3">
+      <c r="BD15" s="3">
         <v>22283603.603603605</v>
       </c>
-      <c r="AY15" s="3">
+      <c r="BE15" s="3">
         <v>606216.21621621598</v>
       </c>
-      <c r="AZ15" s="3">
+      <c r="BF15" s="3">
+        <v>19639.639639640001</v>
+      </c>
+      <c r="BG15" s="3">
         <v>3639</v>
       </c>
-      <c r="BA15" s="3">
+      <c r="BH15" s="3">
         <v>3492</v>
       </c>
-      <c r="BB15" s="3">
+      <c r="BI15" s="3">
         <v>3753</v>
       </c>
-      <c r="BC15" s="3">
+      <c r="BJ15" s="3">
         <v>3758</v>
       </c>
-      <c r="BD15" s="3">
+      <c r="BK15" s="3">
         <v>3447</v>
       </c>
-      <c r="BE15" s="3">
+      <c r="BL15" s="3">
         <v>3755</v>
       </c>
-      <c r="BF15" s="1">
+      <c r="BM15" s="3">
         <v>3530</v>
       </c>
+      <c r="BN15" s="3">
+        <v>4626</v>
+      </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
@@ -2642,31 +2934,31 @@
         <v>190066185.58074287</v>
       </c>
       <c r="J16" s="3">
+        <v>207002554.99264345</v>
+      </c>
+      <c r="K16" s="3">
         <v>274774.77477477503</v>
       </c>
-      <c r="K16" s="3">
+      <c r="L16" s="3">
         <v>235765.76576576501</v>
       </c>
-      <c r="L16" s="3">
+      <c r="M16" s="3">
         <v>3336936.936936934</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>3814414.4144144142</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="3">
         <v>176397306.3063063</v>
       </c>
-      <c r="O16" s="3">
+      <c r="P16" s="3">
         <v>147025337.83783782</v>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="3">
         <v>103184684.68468469</v>
       </c>
-      <c r="Q16" s="3">
-        <v>0</v>
-      </c>
       <c r="R16" s="3">
-        <v>0</v>
+        <v>91817117.117117122</v>
       </c>
       <c r="S16" s="3">
         <v>0</v>
@@ -2681,115 +2973,139 @@
         <v>0</v>
       </c>
       <c r="W16" s="3">
+        <v>0</v>
+      </c>
+      <c r="X16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
         <v>1</v>
       </c>
-      <c r="X16" s="3">
+      <c r="Z16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="3">
         <v>14</v>
       </c>
-      <c r="Y16" s="3">
+      <c r="AB16" s="3">
         <v>18</v>
       </c>
-      <c r="Z16" s="3">
+      <c r="AC16" s="3">
         <v>53</v>
       </c>
-      <c r="AA16" s="3">
+      <c r="AD16" s="3">
         <v>40</v>
       </c>
-      <c r="AB16" s="3">
+      <c r="AE16" s="3">
         <v>27</v>
       </c>
-      <c r="AC16" s="3">
+      <c r="AF16" s="3">
         <v>37</v>
       </c>
-      <c r="AD16" s="3">
+      <c r="AG16" s="3">
         <v>49</v>
       </c>
-      <c r="AE16" s="3">
+      <c r="AH16" s="3">
+        <v>51</v>
+      </c>
+      <c r="AI16" s="3">
         <v>8792792.7927927915</v>
       </c>
-      <c r="AF16" s="3">
+      <c r="AJ16" s="3">
         <v>8823153.1531531513</v>
       </c>
-      <c r="AG16" s="3">
+      <c r="AK16" s="3">
         <v>10794594.594594592</v>
       </c>
-      <c r="AH16" s="3">
+      <c r="AL16" s="3">
         <v>9611711.7117117122</v>
       </c>
-      <c r="AI16" s="3">
+      <c r="AM16" s="3">
         <v>77414864.864864871</v>
       </c>
-      <c r="AJ16" s="3">
+      <c r="AN16" s="3">
         <v>107169987.38738739</v>
       </c>
-      <c r="AK16" s="3">
+      <c r="AO16" s="3">
         <v>34478153.153153151</v>
       </c>
-      <c r="AL16" s="3">
+      <c r="AP16" s="3">
+        <v>17452927.927927926</v>
+      </c>
+      <c r="AQ16" s="3">
         <v>71787887.38738738</v>
       </c>
-      <c r="AM16" s="3">
+      <c r="AR16" s="3">
         <v>66822295.045045041</v>
       </c>
-      <c r="AN16" s="3">
+      <c r="AS16" s="3">
         <v>81646585.585585579</v>
       </c>
-      <c r="AO16" s="3">
+      <c r="AT16" s="3">
         <v>75973052.252252251</v>
       </c>
-      <c r="AP16" s="3">
+      <c r="AU16" s="3">
         <v>76229475.675675675</v>
       </c>
-      <c r="AQ16" s="3">
+      <c r="AV16" s="3">
         <v>72418261.261261269</v>
       </c>
-      <c r="AR16" s="3">
+      <c r="AW16" s="3">
         <v>72137783.783783779</v>
       </c>
-      <c r="AS16" s="3">
+      <c r="AX16" s="3">
+        <v>69856966.216216221</v>
+      </c>
+      <c r="AY16" s="3">
         <v>8465099.0990991015</v>
       </c>
-      <c r="AT16" s="3">
+      <c r="AZ16" s="3">
         <v>7592477.4774774779</v>
       </c>
-      <c r="AU16" s="3">
+      <c r="BA16" s="3">
         <v>12520180.180180177</v>
       </c>
-      <c r="AV16" s="3">
+      <c r="BB16" s="3">
         <v>9154144.1441441439</v>
       </c>
-      <c r="AW16" s="3">
+      <c r="BC16" s="3">
         <v>18817477.477477476</v>
       </c>
-      <c r="AX16" s="3">
+      <c r="BD16" s="3">
         <v>20870540.540540539</v>
       </c>
-      <c r="AY16" s="3">
+      <c r="BE16" s="3">
         <v>31856576.576576576</v>
       </c>
-      <c r="AZ16" s="3">
+      <c r="BF16" s="3">
+        <v>15913873.873873873</v>
+      </c>
+      <c r="BG16" s="3">
         <v>3401</v>
       </c>
-      <c r="BA16" s="3">
+      <c r="BH16" s="3">
         <v>3453</v>
       </c>
-      <c r="BB16" s="3">
+      <c r="BI16" s="3">
         <v>3717</v>
       </c>
-      <c r="BC16" s="3">
+      <c r="BJ16" s="3">
         <v>3786</v>
       </c>
-      <c r="BD16" s="3">
+      <c r="BK16" s="3">
         <v>5507</v>
       </c>
-      <c r="BE16" s="3">
+      <c r="BL16" s="3">
         <v>3822</v>
       </c>
-      <c r="BF16" s="1">
+      <c r="BM16" s="3">
         <v>3805</v>
       </c>
+      <c r="BN16" s="3">
+        <v>6405</v>
+      </c>
     </row>
-    <row r="17" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
@@ -2818,154 +3134,178 @@
         <v>123579774.40923691</v>
       </c>
       <c r="J17" s="3">
+        <v>140700362.30831701</v>
+      </c>
+      <c r="K17" s="3">
         <v>97747.747747747999</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>321936.93693693797</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2075675.675675675</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1740540.5405405399</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>471171.17117117101</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2105405.405405404</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1352702.702702703</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
       <c r="R17" s="3">
-        <v>0</v>
+        <v>5496396.3963963967</v>
       </c>
       <c r="S17" s="3">
         <v>0</v>
       </c>
       <c r="T17" s="3">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
         <v>1</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
       <c r="W17" s="3">
         <v>0</v>
       </c>
       <c r="X17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="3">
         <v>13</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AB17" s="3">
         <v>68</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AC17" s="3">
         <v>66</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AD17" s="3">
         <v>31</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AE17" s="3">
         <v>17</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AF17" s="3">
         <v>48</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AG17" s="3">
         <v>25</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AH17" s="3">
+        <v>25</v>
+      </c>
+      <c r="AI17" s="3">
         <v>18822972.97297297</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AJ17" s="3">
         <v>12843108.108108109</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AK17" s="3">
         <v>11534234.234234236</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AL17" s="3">
         <v>9440540.5405405313</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AM17" s="3">
         <v>24471171.171171173</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AN17" s="3">
         <v>34308108.108108103</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AO17" s="3">
         <v>20226576.576576576</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AP17" s="3">
+        <v>23154054.054054055</v>
+      </c>
+      <c r="AQ17" s="3">
         <v>47596881.081081077</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AR17" s="3">
         <v>48907360.360360362</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AS17" s="3">
         <v>61340953.153153151</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AT17" s="3">
         <v>51499123.423423424</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AU17" s="3">
         <v>54383216.216216214</v>
       </c>
-      <c r="AQ17" s="3">
+      <c r="AV17" s="3">
         <v>55297000</v>
       </c>
-      <c r="AR17" s="3">
+      <c r="AW17" s="3">
         <v>53152927.927927926</v>
       </c>
-      <c r="AS17" s="3">
+      <c r="AX17" s="3">
+        <v>55015828.828828834</v>
+      </c>
+      <c r="AY17" s="3">
         <v>14111153.153153151</v>
       </c>
-      <c r="AT17" s="3">
+      <c r="AZ17" s="3">
         <v>12608378.378378378</v>
       </c>
-      <c r="AU17" s="3">
+      <c r="BA17" s="3">
         <v>11307387.387387387</v>
       </c>
-      <c r="AV17" s="3">
+      <c r="BB17" s="3">
         <v>9557927.9279279206</v>
       </c>
-      <c r="AW17" s="3">
+      <c r="BC17" s="3">
         <v>24743603.603603605</v>
       </c>
-      <c r="AX17" s="3">
+      <c r="BD17" s="3">
         <v>29474864.864864863</v>
       </c>
-      <c r="AY17" s="3">
+      <c r="BE17" s="3">
         <v>20739099.0990991</v>
       </c>
-      <c r="AZ17" s="3">
+      <c r="BF17" s="3">
+        <v>27229909.909909911</v>
+      </c>
+      <c r="BG17" s="3">
         <v>2548</v>
       </c>
-      <c r="BA17" s="3">
+      <c r="BH17" s="3">
         <v>2563</v>
       </c>
-      <c r="BB17" s="3">
+      <c r="BI17" s="3">
         <v>3006</v>
       </c>
-      <c r="BC17" s="3">
+      <c r="BJ17" s="3">
         <v>2932</v>
       </c>
-      <c r="BD17" s="3">
+      <c r="BK17" s="3">
         <v>3025</v>
       </c>
-      <c r="BE17" s="3">
+      <c r="BL17" s="3">
         <v>2859</v>
       </c>
-      <c r="BF17" s="1">
+      <c r="BM17" s="3">
         <v>2808</v>
       </c>
+      <c r="BN17" s="3">
+        <v>5952</v>
+      </c>
     </row>
-    <row r="18" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
@@ -2994,154 +3334,178 @@
         <v>445756632.36136365</v>
       </c>
       <c r="J18" s="3">
+        <v>475053291.03286129</v>
+      </c>
+      <c r="K18" s="3">
         <v>297825005.4054054</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>593172914.41441441</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>432353816.21621621</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>584661011.71171176</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4777485.5855855877</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8999099.0990991015</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7280018.9189189225</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
-        <v>0</v>
+        <v>6318918.9189189253</v>
       </c>
       <c r="S18" s="3">
         <v>0</v>
       </c>
       <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>4</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>3</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>3</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
+        <v>2</v>
+      </c>
+      <c r="AA18" s="3">
         <v>378</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AB18" s="3">
         <v>473</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AC18" s="3">
         <v>677</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AD18" s="3">
         <v>468</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AE18" s="3">
         <v>694</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AF18" s="3">
         <v>1016</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AG18" s="3">
         <v>1015</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AH18" s="3">
+        <v>836</v>
+      </c>
+      <c r="AI18" s="3">
         <v>64616126.126126125</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AJ18" s="3">
         <v>57526216.216216214</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AK18" s="3">
         <v>68259909.909909919</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AL18" s="3">
         <v>79598198.198198199</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AM18" s="3">
         <v>137399782.88288289</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AN18" s="3">
         <v>143875450.45045045</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AO18" s="3">
         <v>181679764.86486486</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AP18" s="3">
+        <v>177102027.02702704</v>
+      </c>
+      <c r="AQ18" s="3">
         <v>247552630.63063061</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AR18" s="3">
         <v>253424531.53153151</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AS18" s="3">
         <v>288917252.25225222</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AT18" s="3">
         <v>235132115.31531534</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AU18" s="3">
         <v>268380423.42342341</v>
       </c>
-      <c r="AQ18" s="3">
+      <c r="AV18" s="3">
         <v>259011018.01801801</v>
       </c>
-      <c r="AR18" s="3">
+      <c r="AW18" s="3">
         <v>279009504.5045045</v>
       </c>
-      <c r="AS18" s="3">
+      <c r="AX18" s="3">
+        <v>285670135.13513511</v>
+      </c>
+      <c r="AY18" s="3">
         <v>55377549.54954955</v>
       </c>
-      <c r="AT18" s="3">
+      <c r="AZ18" s="3">
         <v>53618441.441441439</v>
       </c>
-      <c r="AU18" s="3">
+      <c r="BA18" s="3">
         <v>56583513.51351352</v>
       </c>
-      <c r="AV18" s="3">
+      <c r="BB18" s="3">
         <v>68058918.918918923</v>
       </c>
-      <c r="AW18" s="3">
+      <c r="BC18" s="3">
         <v>137662567.56756756</v>
       </c>
-      <c r="AX18" s="3">
+      <c r="BD18" s="3">
         <v>140834549.54954955</v>
       </c>
-      <c r="AY18" s="3">
+      <c r="BE18" s="3">
         <v>208183063.06306309</v>
       </c>
-      <c r="AZ18" s="3">
+      <c r="BF18" s="3">
+        <v>192270718.91891891</v>
+      </c>
+      <c r="BG18" s="3">
         <v>6609</v>
       </c>
-      <c r="BA18" s="3">
+      <c r="BH18" s="3">
         <v>6595</v>
       </c>
-      <c r="BB18" s="3">
+      <c r="BI18" s="3">
         <v>6748</v>
       </c>
-      <c r="BC18" s="3">
+      <c r="BJ18" s="3">
         <v>9658</v>
       </c>
-      <c r="BD18" s="3">
+      <c r="BK18" s="3">
         <v>8834</v>
       </c>
-      <c r="BE18" s="3">
+      <c r="BL18" s="3">
         <v>7861</v>
       </c>
-      <c r="BF18" s="1">
+      <c r="BM18" s="3">
         <v>7168</v>
       </c>
+      <c r="BN18" s="3">
+        <v>10672</v>
+      </c>
     </row>
-    <row r="19" spans="1:58" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
@@ -3170,31 +3534,31 @@
         <v>239444971.9093622</v>
       </c>
       <c r="J19" s="3">
+        <v>240860680.16253296</v>
+      </c>
+      <c r="K19" s="3">
         <v>1299729.7297297299</v>
       </c>
-      <c r="K19" s="3">
+      <c r="L19" s="3">
         <v>620180.18018018</v>
       </c>
-      <c r="L19" s="3">
+      <c r="M19" s="3">
         <v>1156756.756756756</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="3">
         <v>6994144.1441441393</v>
       </c>
-      <c r="N19" s="3">
+      <c r="O19" s="3">
         <v>4467567.567567572</v>
       </c>
-      <c r="O19" s="3">
+      <c r="P19" s="3">
         <v>1938738.738738738</v>
       </c>
-      <c r="P19" s="3">
+      <c r="Q19" s="3">
         <v>1779947.7477477491</v>
       </c>
-      <c r="Q19" s="3">
-        <v>0</v>
-      </c>
       <c r="R19" s="3">
-        <v>0</v>
+        <v>1682882.882882881</v>
       </c>
       <c r="S19" s="3">
         <v>0</v>
@@ -3212,109 +3576,133 @@
         <v>0</v>
       </c>
       <c r="X19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="3">
         <v>25</v>
       </c>
-      <c r="Y19" s="3">
+      <c r="AB19" s="3">
         <v>18</v>
       </c>
-      <c r="Z19" s="3">
+      <c r="AC19" s="3">
         <v>30</v>
       </c>
-      <c r="AA19" s="3">
+      <c r="AD19" s="3">
         <v>37</v>
       </c>
-      <c r="AB19" s="3">
+      <c r="AE19" s="3">
         <v>39</v>
       </c>
-      <c r="AC19" s="3">
+      <c r="AF19" s="3">
         <v>28</v>
       </c>
-      <c r="AD19" s="3">
+      <c r="AG19" s="3">
         <v>40</v>
       </c>
-      <c r="AE19" s="3">
+      <c r="AH19" s="3">
+        <v>41</v>
+      </c>
+      <c r="AI19" s="3">
         <v>28883783.783783782</v>
       </c>
-      <c r="AF19" s="3">
+      <c r="AJ19" s="3">
         <v>42477612.612612613</v>
       </c>
-      <c r="AG19" s="3">
+      <c r="AK19" s="3">
         <v>44288513.513513513</v>
       </c>
-      <c r="AH19" s="3">
+      <c r="AL19" s="3">
         <v>39225675.675675675</v>
       </c>
-      <c r="AI19" s="3">
+      <c r="AM19" s="3">
         <v>51458783.783783786</v>
       </c>
-      <c r="AJ19" s="3">
+      <c r="AN19" s="3">
         <v>44963063.063063063</v>
       </c>
-      <c r="AK19" s="3">
+      <c r="AO19" s="3">
         <v>52455705.40540541</v>
       </c>
-      <c r="AL19" s="3">
+      <c r="AP19" s="3">
+        <v>51436936.936936937</v>
+      </c>
+      <c r="AQ19" s="3">
         <v>109155265.76576576</v>
       </c>
-      <c r="AM19" s="3">
+      <c r="AR19" s="3">
         <v>106279961.7117117</v>
       </c>
-      <c r="AN19" s="3">
+      <c r="AS19" s="3">
         <v>120641801.8018018</v>
       </c>
-      <c r="AO19" s="3">
+      <c r="AT19" s="3">
         <v>99386009.009009004</v>
       </c>
-      <c r="AP19" s="3">
+      <c r="AU19" s="3">
         <v>99723738.738738731</v>
       </c>
-      <c r="AQ19" s="3">
+      <c r="AV19" s="3">
         <v>89829945.945945948</v>
       </c>
-      <c r="AR19" s="3">
+      <c r="AW19" s="3">
         <v>83526045.045045033</v>
       </c>
-      <c r="AS19" s="3">
+      <c r="AX19" s="3">
+        <v>80156396.396396399</v>
+      </c>
+      <c r="AY19" s="3">
         <v>34262927.927927926</v>
       </c>
-      <c r="AT19" s="3">
+      <c r="AZ19" s="3">
         <v>39493333.333333336</v>
       </c>
-      <c r="AU19" s="3">
+      <c r="BA19" s="3">
         <v>35223603.603603601</v>
       </c>
-      <c r="AV19" s="3">
+      <c r="BB19" s="3">
         <v>42599729.729729727</v>
       </c>
-      <c r="AW19" s="3">
+      <c r="BC19" s="3">
         <v>50633198.198198199</v>
       </c>
-      <c r="AX19" s="3">
+      <c r="BD19" s="3">
         <v>40236396.396396399</v>
       </c>
-      <c r="AY19" s="3">
+      <c r="BE19" s="3">
         <v>45674504.504504502</v>
       </c>
-      <c r="AZ19" s="3">
+      <c r="BF19" s="3">
+        <v>49132522.522522517</v>
+      </c>
+      <c r="BG19" s="3">
         <v>3792</v>
       </c>
-      <c r="BA19" s="3">
+      <c r="BH19" s="3">
         <v>3750</v>
       </c>
-      <c r="BB19" s="3">
+      <c r="BI19" s="3">
         <v>3745</v>
       </c>
-      <c r="BC19" s="3">
+      <c r="BJ19" s="3">
         <v>3930</v>
       </c>
-      <c r="BD19" s="3">
+      <c r="BK19" s="3">
         <v>3907</v>
       </c>
-      <c r="BE19" s="3">
+      <c r="BL19" s="3">
         <v>4082</v>
       </c>
-      <c r="BF19" s="1">
+      <c r="BM19" s="3">
         <v>4032</v>
+      </c>
+      <c r="BN19" s="3">
+        <v>4211</v>
       </c>
     </row>
   </sheetData>
